--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8b65b6adf7979/桌面/Github File/IC_Design_Laboratory/HW5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="11_1B85D0BDD370594FA3B82111595ED87656CB84C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF52878F-A805-4B1E-A268-8FD1D9506C7C}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="11_1B85D0BDD370594FA3B82111595ED87656CB84C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B55C661F-0CC7-4A37-923C-6625925A433E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="3092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="3125">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -8832,9 +8832,6 @@
   </si>
   <si>
     <t>0.47236655274101480017634457908570766448974609375</t>
-  </si>
-  <si>
-    <t>531837457726680</t>
   </si>
   <si>
     <t>0.4798052435596775304390357660235938813242147370504269939226478799473997045225714644117531988220930455</t>
@@ -9325,6 +9322,142 @@
   </si>
   <si>
     <t>插值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1538472748139629</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mul 1/24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>add 1/6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mul (x-a)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>add 1/2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>add 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> mul expa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2731*16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1*2^21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1*2^26</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;26</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1*2^30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>495312&lt;&lt;30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lut point a</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>對齊小數點</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp(a)真值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp(x)誤差</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>求 EXP(982)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp(a)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp(x)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATAFLOW設計: 這部分錯誤, 因為對其不是左移四位, 應為六位, 直接更新在code上</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9333,12 +9466,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="195" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="197" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="200" formatCode="0.0000%"/>
-    <numFmt numFmtId="203" formatCode="0.0000000%"/>
-    <numFmt numFmtId="205" formatCode="0.0000000"/>
-    <numFmt numFmtId="206" formatCode="0.000000"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="178" formatCode="0.0000%"/>
+    <numFmt numFmtId="179" formatCode="0.0000000%"/>
+    <numFmt numFmtId="180" formatCode="0.0000000"/>
+    <numFmt numFmtId="181" formatCode="0.000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -9384,7 +9517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -9444,6 +9577,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -9451,22 +9593,28 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="197" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="206" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -9774,7 +9922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1048"/>
+  <dimension ref="A1:H1073"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
@@ -9783,12 +9931,12 @@
     <col min="4" max="4" width="27.8984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.8984375" customWidth="1"/>
-    <col min="7" max="7" width="11.8984375" customWidth="1"/>
+    <col min="7" max="7" width="49.8984375" customWidth="1"/>
     <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9804,8 +9952,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="8" t="s">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -9822,10 +9973,14 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>3075</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3074</v>
+      </c>
+      <c r="G2" s="2">
+        <f>E2-G1</f>
+        <v>-412572841297000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -9841,8 +9996,12 @@
       <c r="E3" s="3">
         <v>1143630250473350</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G23" si="0">E3-G2</f>
+        <v>1556203091770350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -9858,8 +10017,12 @@
       <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="2">
+        <f t="shared" si="0"/>
+        <v>-394563285381620</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -9875,8 +10038,12 @@
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="2">
+        <f t="shared" si="0"/>
+        <v>1574496256924050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -9892,8 +10059,12 @@
       <c r="E6" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="2">
+        <f t="shared" si="0"/>
+        <v>-375982044793950</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -9909,8 +10080,12 @@
       <c r="E7" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="2">
+        <f t="shared" si="0"/>
+        <v>1593370109473680</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -9926,8 +10101,12 @@
       <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>-356810972314470</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -9943,8 +10122,12 @@
       <c r="E9" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>1612843082415870</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -9960,8 +10143,12 @@
       <c r="E10" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="2">
+        <f t="shared" si="0"/>
+        <v>-337031344669070</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -9977,8 +10164,12 @@
       <c r="E11" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="2">
+        <f t="shared" si="0"/>
+        <v>1632934193873380</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -9994,8 +10185,12 @@
       <c r="E12" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="2">
+        <f t="shared" si="0"/>
+        <v>-316623844243150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -10011,8 +10206,12 @@
       <c r="E13" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="2">
+        <f t="shared" si="0"/>
+        <v>1653663065669000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -10028,8 +10227,12 @@
       <c r="E14" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="2">
+        <f t="shared" si="0"/>
+        <v>-295568540215170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -10045,8 +10248,12 @@
       <c r="E15" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="2">
+        <f t="shared" si="0"/>
+        <v>1675049942489020</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -10062,8 +10269,12 @@
       <c r="E16" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G16" s="2">
+        <f t="shared" si="0"/>
+        <v>-273844869091410</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -10079,8 +10290,12 @@
       <c r="E17" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G17" s="2">
+        <f t="shared" si="0"/>
+        <v>1697115711655080</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -10096,8 +10311,12 @@
       <c r="E18" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G18" s="2">
+        <f t="shared" si="0"/>
+        <v>-251431614622790</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -10113,8 +10332,12 @@
       <c r="E19" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G19" s="2">
+        <f t="shared" si="0"/>
+        <v>1719881923523550</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -10130,8 +10353,12 @@
       <c r="E20" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G20" s="2">
+        <f t="shared" si="0"/>
+        <v>-228306887084200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -10147,8 +10374,12 @@
       <c r="E21" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G21" s="2">
+        <f t="shared" si="0"/>
+        <v>1743370812532580</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -10164,8 +10395,12 @@
       <c r="E22" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G22" s="2">
+        <f t="shared" si="0"/>
+        <v>-204448101896040</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -10181,8 +10416,12 @@
       <c r="E23" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G23" s="2">
+        <f t="shared" si="0"/>
+        <v>1767605318917110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -10199,7 +10438,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -10216,7 +10455,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -10233,7 +10472,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -10250,7 +10489,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -10267,7 +10506,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -10284,7 +10523,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -10301,7 +10540,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -10318,7 +10557,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -10913,7 +11152,7 @@
         <v>197</v>
       </c>
       <c r="F66" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -12004,7 +12243,7 @@
         <v>389</v>
       </c>
       <c r="F130" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -13095,7 +13334,7 @@
         <v>581</v>
       </c>
       <c r="F194" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
@@ -14186,7 +14425,7 @@
         <v>773</v>
       </c>
       <c r="F258" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -15277,7 +15516,7 @@
         <v>965</v>
       </c>
       <c r="F322" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
@@ -16368,7 +16607,7 @@
         <v>1157</v>
       </c>
       <c r="F386" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.3">
@@ -17459,7 +17698,7 @@
         <v>1349</v>
       </c>
       <c r="F450" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.3">
@@ -18550,7 +18789,7 @@
         <v>1541</v>
       </c>
       <c r="F514" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.3">
@@ -19641,7 +19880,7 @@
         <v>1733</v>
       </c>
       <c r="F578" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.3">
@@ -20732,7 +20971,7 @@
         <v>1925</v>
       </c>
       <c r="F642" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.3">
@@ -21823,7 +22062,7 @@
         <v>2117</v>
       </c>
       <c r="F706" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.3">
@@ -22914,7 +23153,7 @@
         <v>2309</v>
       </c>
       <c r="F770" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.3">
@@ -24005,7 +24244,7 @@
         <v>2501</v>
       </c>
       <c r="F834" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.3">
@@ -25096,7 +25335,7 @@
         <v>2693</v>
       </c>
       <c r="F898" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.3">
@@ -26187,7 +26426,7 @@
         <v>2885</v>
       </c>
       <c r="F962" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.3">
@@ -26458,8 +26697,8 @@
       <c r="D978" t="s">
         <v>2932</v>
       </c>
-      <c r="E978" s="2" t="s">
-        <v>2933</v>
+      <c r="E978" s="9">
+        <v>531837457726680</v>
       </c>
     </row>
     <row r="979" spans="1:5" x14ac:dyDescent="0.3">
@@ -26470,13 +26709,13 @@
         <v>-0.734375</v>
       </c>
       <c r="C979" t="s">
+        <v>2933</v>
+      </c>
+      <c r="D979" t="s">
         <v>2934</v>
       </c>
-      <c r="D979" t="s">
+      <c r="E979" s="2" t="s">
         <v>2935</v>
-      </c>
-      <c r="E979" s="2" t="s">
-        <v>2936</v>
       </c>
     </row>
     <row r="980" spans="1:5" x14ac:dyDescent="0.3">
@@ -26487,13 +26726,13 @@
         <v>-0.71875</v>
       </c>
       <c r="C980" t="s">
+        <v>2936</v>
+      </c>
+      <c r="D980" t="s">
         <v>2937</v>
       </c>
-      <c r="D980" t="s">
+      <c r="E980" s="2" t="s">
         <v>2938</v>
-      </c>
-      <c r="E980" s="2" t="s">
-        <v>2939</v>
       </c>
     </row>
     <row r="981" spans="1:5" x14ac:dyDescent="0.3">
@@ -26504,13 +26743,13 @@
         <v>-0.703125</v>
       </c>
       <c r="C981" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D981" t="s">
         <v>2940</v>
       </c>
-      <c r="D981" t="s">
+      <c r="E981" s="2" t="s">
         <v>2941</v>
-      </c>
-      <c r="E981" s="2" t="s">
-        <v>2942</v>
       </c>
     </row>
     <row r="982" spans="1:5" x14ac:dyDescent="0.3">
@@ -26521,13 +26760,13 @@
         <v>-0.6875</v>
       </c>
       <c r="C982" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D982" t="s">
         <v>2943</v>
       </c>
-      <c r="D982" t="s">
+      <c r="E982" s="2" t="s">
         <v>2944</v>
-      </c>
-      <c r="E982" s="2" t="s">
-        <v>2945</v>
       </c>
     </row>
     <row r="983" spans="1:5" x14ac:dyDescent="0.3">
@@ -26538,13 +26777,13 @@
         <v>-0.671875</v>
       </c>
       <c r="C983" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D983" t="s">
         <v>2946</v>
       </c>
-      <c r="D983" t="s">
+      <c r="E983" s="2" t="s">
         <v>2947</v>
-      </c>
-      <c r="E983" s="2" t="s">
-        <v>2948</v>
       </c>
     </row>
     <row r="984" spans="1:5" x14ac:dyDescent="0.3">
@@ -26555,13 +26794,13 @@
         <v>-0.65625</v>
       </c>
       <c r="C984" t="s">
+        <v>2948</v>
+      </c>
+      <c r="D984" t="s">
         <v>2949</v>
       </c>
-      <c r="D984" t="s">
+      <c r="E984" s="2" t="s">
         <v>2950</v>
-      </c>
-      <c r="E984" s="2" t="s">
-        <v>2951</v>
       </c>
     </row>
     <row r="985" spans="1:5" x14ac:dyDescent="0.3">
@@ -26572,13 +26811,13 @@
         <v>-0.640625</v>
       </c>
       <c r="C985" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D985" t="s">
         <v>2952</v>
       </c>
-      <c r="D985" t="s">
+      <c r="E985" s="2" t="s">
         <v>2953</v>
-      </c>
-      <c r="E985" s="2" t="s">
-        <v>2954</v>
       </c>
     </row>
     <row r="986" spans="1:5" x14ac:dyDescent="0.3">
@@ -26589,13 +26828,13 @@
         <v>-0.625</v>
       </c>
       <c r="C986" t="s">
+        <v>2954</v>
+      </c>
+      <c r="D986" t="s">
         <v>2955</v>
       </c>
-      <c r="D986" t="s">
+      <c r="E986" s="2" t="s">
         <v>2956</v>
-      </c>
-      <c r="E986" s="2" t="s">
-        <v>2957</v>
       </c>
     </row>
     <row r="987" spans="1:5" x14ac:dyDescent="0.3">
@@ -26606,13 +26845,13 @@
         <v>-0.609375</v>
       </c>
       <c r="C987" t="s">
+        <v>2957</v>
+      </c>
+      <c r="D987" t="s">
         <v>2958</v>
       </c>
-      <c r="D987" t="s">
+      <c r="E987" s="2" t="s">
         <v>2959</v>
-      </c>
-      <c r="E987" s="2" t="s">
-        <v>2960</v>
       </c>
     </row>
     <row r="988" spans="1:5" x14ac:dyDescent="0.3">
@@ -26623,13 +26862,13 @@
         <v>-0.59375</v>
       </c>
       <c r="C988" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D988" t="s">
         <v>2961</v>
       </c>
-      <c r="D988" t="s">
+      <c r="E988" s="2" t="s">
         <v>2962</v>
-      </c>
-      <c r="E988" s="2" t="s">
-        <v>2963</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.3">
@@ -26640,13 +26879,13 @@
         <v>-0.578125</v>
       </c>
       <c r="C989" t="s">
+        <v>2963</v>
+      </c>
+      <c r="D989" t="s">
         <v>2964</v>
       </c>
-      <c r="D989" t="s">
+      <c r="E989" s="2" t="s">
         <v>2965</v>
-      </c>
-      <c r="E989" s="2" t="s">
-        <v>2966</v>
       </c>
     </row>
     <row r="990" spans="1:5" x14ac:dyDescent="0.3">
@@ -26657,13 +26896,13 @@
         <v>-0.5625</v>
       </c>
       <c r="C990" t="s">
+        <v>2966</v>
+      </c>
+      <c r="D990" t="s">
         <v>2967</v>
       </c>
-      <c r="D990" t="s">
+      <c r="E990" s="2" t="s">
         <v>2968</v>
-      </c>
-      <c r="E990" s="2" t="s">
-        <v>2969</v>
       </c>
     </row>
     <row r="991" spans="1:5" x14ac:dyDescent="0.3">
@@ -26674,13 +26913,13 @@
         <v>-0.546875</v>
       </c>
       <c r="C991" t="s">
+        <v>2969</v>
+      </c>
+      <c r="D991" t="s">
         <v>2970</v>
       </c>
-      <c r="D991" t="s">
+      <c r="E991" s="2" t="s">
         <v>2971</v>
-      </c>
-      <c r="E991" s="2" t="s">
-        <v>2972</v>
       </c>
     </row>
     <row r="992" spans="1:5" x14ac:dyDescent="0.3">
@@ -26691,13 +26930,13 @@
         <v>-0.53125</v>
       </c>
       <c r="C992" t="s">
+        <v>2972</v>
+      </c>
+      <c r="D992" t="s">
         <v>2973</v>
       </c>
-      <c r="D992" t="s">
+      <c r="E992" s="2" t="s">
         <v>2974</v>
-      </c>
-      <c r="E992" s="2" t="s">
-        <v>2975</v>
       </c>
     </row>
     <row r="993" spans="1:5" x14ac:dyDescent="0.3">
@@ -26708,13 +26947,13 @@
         <v>-0.515625</v>
       </c>
       <c r="C993" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D993" t="s">
         <v>2976</v>
       </c>
-      <c r="D993" t="s">
+      <c r="E993" s="2" t="s">
         <v>2977</v>
-      </c>
-      <c r="E993" s="2" t="s">
-        <v>2978</v>
       </c>
     </row>
     <row r="994" spans="1:5" x14ac:dyDescent="0.3">
@@ -26725,13 +26964,13 @@
         <v>-0.5</v>
       </c>
       <c r="C994" t="s">
+        <v>2978</v>
+      </c>
+      <c r="D994" t="s">
         <v>2979</v>
       </c>
-      <c r="D994" t="s">
+      <c r="E994" s="2" t="s">
         <v>2980</v>
-      </c>
-      <c r="E994" s="2" t="s">
-        <v>2981</v>
       </c>
     </row>
     <row r="995" spans="1:5" x14ac:dyDescent="0.3">
@@ -26742,13 +26981,13 @@
         <v>-0.484375</v>
       </c>
       <c r="C995" t="s">
+        <v>2981</v>
+      </c>
+      <c r="D995" t="s">
         <v>2982</v>
       </c>
-      <c r="D995" t="s">
+      <c r="E995" s="2" t="s">
         <v>2983</v>
-      </c>
-      <c r="E995" s="2" t="s">
-        <v>2984</v>
       </c>
     </row>
     <row r="996" spans="1:5" x14ac:dyDescent="0.3">
@@ -26759,13 +26998,13 @@
         <v>-0.46875</v>
       </c>
       <c r="C996" t="s">
+        <v>2984</v>
+      </c>
+      <c r="D996" t="s">
         <v>2985</v>
       </c>
-      <c r="D996" t="s">
+      <c r="E996" s="2" t="s">
         <v>2986</v>
-      </c>
-      <c r="E996" s="2" t="s">
-        <v>2987</v>
       </c>
     </row>
     <row r="997" spans="1:5" x14ac:dyDescent="0.3">
@@ -26776,13 +27015,13 @@
         <v>-0.453125</v>
       </c>
       <c r="C997" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D997" t="s">
         <v>2988</v>
       </c>
-      <c r="D997" t="s">
+      <c r="E997" s="2" t="s">
         <v>2989</v>
-      </c>
-      <c r="E997" s="2" t="s">
-        <v>2990</v>
       </c>
     </row>
     <row r="998" spans="1:5" x14ac:dyDescent="0.3">
@@ -26793,13 +27032,13 @@
         <v>-0.4375</v>
       </c>
       <c r="C998" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D998" t="s">
         <v>2991</v>
       </c>
-      <c r="D998" t="s">
+      <c r="E998" s="2" t="s">
         <v>2992</v>
-      </c>
-      <c r="E998" s="2" t="s">
-        <v>2993</v>
       </c>
     </row>
     <row r="999" spans="1:5" x14ac:dyDescent="0.3">
@@ -26810,13 +27049,13 @@
         <v>-0.421875</v>
       </c>
       <c r="C999" t="s">
+        <v>2993</v>
+      </c>
+      <c r="D999" t="s">
         <v>2994</v>
       </c>
-      <c r="D999" t="s">
+      <c r="E999" s="2" t="s">
         <v>2995</v>
-      </c>
-      <c r="E999" s="2" t="s">
-        <v>2996</v>
       </c>
     </row>
     <row r="1000" spans="1:5" x14ac:dyDescent="0.3">
@@ -26827,13 +27066,13 @@
         <v>-0.40625</v>
       </c>
       <c r="C1000" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D1000" t="s">
         <v>2997</v>
       </c>
-      <c r="D1000" t="s">
+      <c r="E1000" s="2" t="s">
         <v>2998</v>
-      </c>
-      <c r="E1000" s="2" t="s">
-        <v>2999</v>
       </c>
     </row>
     <row r="1001" spans="1:5" x14ac:dyDescent="0.3">
@@ -26844,13 +27083,13 @@
         <v>-0.390625</v>
       </c>
       <c r="C1001" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D1001" t="s">
         <v>3000</v>
       </c>
-      <c r="D1001" t="s">
+      <c r="E1001" s="2" t="s">
         <v>3001</v>
-      </c>
-      <c r="E1001" s="2" t="s">
-        <v>3002</v>
       </c>
     </row>
     <row r="1002" spans="1:5" x14ac:dyDescent="0.3">
@@ -26861,13 +27100,13 @@
         <v>-0.375</v>
       </c>
       <c r="C1002" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D1002" t="s">
         <v>3003</v>
       </c>
-      <c r="D1002" t="s">
+      <c r="E1002" s="2" t="s">
         <v>3004</v>
-      </c>
-      <c r="E1002" s="2" t="s">
-        <v>3005</v>
       </c>
     </row>
     <row r="1003" spans="1:5" x14ac:dyDescent="0.3">
@@ -26878,13 +27117,13 @@
         <v>-0.359375</v>
       </c>
       <c r="C1003" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D1003" t="s">
         <v>3006</v>
       </c>
-      <c r="D1003" t="s">
+      <c r="E1003" s="2" t="s">
         <v>3007</v>
-      </c>
-      <c r="E1003" s="2" t="s">
-        <v>3008</v>
       </c>
     </row>
     <row r="1004" spans="1:5" x14ac:dyDescent="0.3">
@@ -26895,13 +27134,13 @@
         <v>-0.34375</v>
       </c>
       <c r="C1004" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D1004" t="s">
         <v>3009</v>
       </c>
-      <c r="D1004" t="s">
+      <c r="E1004" s="2" t="s">
         <v>3010</v>
-      </c>
-      <c r="E1004" s="2" t="s">
-        <v>3011</v>
       </c>
     </row>
     <row r="1005" spans="1:5" x14ac:dyDescent="0.3">
@@ -26912,13 +27151,13 @@
         <v>-0.328125</v>
       </c>
       <c r="C1005" t="s">
+        <v>3011</v>
+      </c>
+      <c r="D1005" t="s">
         <v>3012</v>
       </c>
-      <c r="D1005" t="s">
+      <c r="E1005" s="2" t="s">
         <v>3013</v>
-      </c>
-      <c r="E1005" s="2" t="s">
-        <v>3014</v>
       </c>
     </row>
     <row r="1006" spans="1:5" x14ac:dyDescent="0.3">
@@ -26929,13 +27168,13 @@
         <v>-0.3125</v>
       </c>
       <c r="C1006" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D1006" t="s">
         <v>3015</v>
       </c>
-      <c r="D1006" t="s">
+      <c r="E1006" s="2" t="s">
         <v>3016</v>
-      </c>
-      <c r="E1006" s="2" t="s">
-        <v>3017</v>
       </c>
     </row>
     <row r="1007" spans="1:5" x14ac:dyDescent="0.3">
@@ -26946,13 +27185,13 @@
         <v>-0.296875</v>
       </c>
       <c r="C1007" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D1007" t="s">
         <v>3018</v>
       </c>
-      <c r="D1007" t="s">
+      <c r="E1007" s="2" t="s">
         <v>3019</v>
-      </c>
-      <c r="E1007" s="2" t="s">
-        <v>3020</v>
       </c>
     </row>
     <row r="1008" spans="1:5" x14ac:dyDescent="0.3">
@@ -26963,13 +27202,13 @@
         <v>-0.28125</v>
       </c>
       <c r="C1008" t="s">
+        <v>3020</v>
+      </c>
+      <c r="D1008" t="s">
         <v>3021</v>
       </c>
-      <c r="D1008" t="s">
+      <c r="E1008" s="2" t="s">
         <v>3022</v>
-      </c>
-      <c r="E1008" s="2" t="s">
-        <v>3023</v>
       </c>
     </row>
     <row r="1009" spans="1:5" x14ac:dyDescent="0.3">
@@ -26980,13 +27219,13 @@
         <v>-0.265625</v>
       </c>
       <c r="C1009" t="s">
+        <v>3023</v>
+      </c>
+      <c r="D1009" t="s">
         <v>3024</v>
       </c>
-      <c r="D1009" t="s">
+      <c r="E1009" s="2" t="s">
         <v>3025</v>
-      </c>
-      <c r="E1009" s="2" t="s">
-        <v>3026</v>
       </c>
     </row>
     <row r="1010" spans="1:5" x14ac:dyDescent="0.3">
@@ -26997,13 +27236,13 @@
         <v>-0.25</v>
       </c>
       <c r="C1010" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D1010" t="s">
         <v>3027</v>
       </c>
-      <c r="D1010" t="s">
+      <c r="E1010" s="2" t="s">
         <v>3028</v>
-      </c>
-      <c r="E1010" s="2" t="s">
-        <v>3029</v>
       </c>
     </row>
     <row r="1011" spans="1:5" x14ac:dyDescent="0.3">
@@ -27014,13 +27253,13 @@
         <v>-0.234375</v>
       </c>
       <c r="C1011" t="s">
+        <v>3029</v>
+      </c>
+      <c r="D1011" t="s">
         <v>3030</v>
       </c>
-      <c r="D1011" t="s">
+      <c r="E1011" s="2" t="s">
         <v>3031</v>
-      </c>
-      <c r="E1011" s="2" t="s">
-        <v>3032</v>
       </c>
     </row>
     <row r="1012" spans="1:5" x14ac:dyDescent="0.3">
@@ -27031,13 +27270,13 @@
         <v>-0.21875</v>
       </c>
       <c r="C1012" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D1012" t="s">
         <v>3033</v>
       </c>
-      <c r="D1012" t="s">
+      <c r="E1012" s="2" t="s">
         <v>3034</v>
-      </c>
-      <c r="E1012" s="2" t="s">
-        <v>3035</v>
       </c>
     </row>
     <row r="1013" spans="1:5" x14ac:dyDescent="0.3">
@@ -27048,13 +27287,13 @@
         <v>-0.203125</v>
       </c>
       <c r="C1013" t="s">
+        <v>3035</v>
+      </c>
+      <c r="D1013" t="s">
         <v>3036</v>
       </c>
-      <c r="D1013" t="s">
+      <c r="E1013" s="2" t="s">
         <v>3037</v>
-      </c>
-      <c r="E1013" s="2" t="s">
-        <v>3038</v>
       </c>
     </row>
     <row r="1014" spans="1:5" x14ac:dyDescent="0.3">
@@ -27065,13 +27304,13 @@
         <v>-0.1875</v>
       </c>
       <c r="C1014" t="s">
+        <v>3038</v>
+      </c>
+      <c r="D1014" t="s">
         <v>3039</v>
       </c>
-      <c r="D1014" t="s">
+      <c r="E1014" s="2" t="s">
         <v>3040</v>
-      </c>
-      <c r="E1014" s="2" t="s">
-        <v>3041</v>
       </c>
     </row>
     <row r="1015" spans="1:5" x14ac:dyDescent="0.3">
@@ -27082,13 +27321,13 @@
         <v>-0.171875</v>
       </c>
       <c r="C1015" t="s">
+        <v>3041</v>
+      </c>
+      <c r="D1015" t="s">
         <v>3042</v>
       </c>
-      <c r="D1015" t="s">
+      <c r="E1015" s="2" t="s">
         <v>3043</v>
-      </c>
-      <c r="E1015" s="2" t="s">
-        <v>3044</v>
       </c>
     </row>
     <row r="1016" spans="1:5" x14ac:dyDescent="0.3">
@@ -27099,13 +27338,13 @@
         <v>-0.15625</v>
       </c>
       <c r="C1016" t="s">
+        <v>3044</v>
+      </c>
+      <c r="D1016" t="s">
         <v>3045</v>
       </c>
-      <c r="D1016" t="s">
+      <c r="E1016" s="2" t="s">
         <v>3046</v>
-      </c>
-      <c r="E1016" s="2" t="s">
-        <v>3047</v>
       </c>
     </row>
     <row r="1017" spans="1:5" x14ac:dyDescent="0.3">
@@ -27116,13 +27355,13 @@
         <v>-0.140625</v>
       </c>
       <c r="C1017" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D1017" t="s">
         <v>3048</v>
       </c>
-      <c r="D1017" t="s">
+      <c r="E1017" s="2" t="s">
         <v>3049</v>
-      </c>
-      <c r="E1017" s="2" t="s">
-        <v>3050</v>
       </c>
     </row>
     <row r="1018" spans="1:5" x14ac:dyDescent="0.3">
@@ -27133,13 +27372,13 @@
         <v>-0.125</v>
       </c>
       <c r="C1018" t="s">
+        <v>3050</v>
+      </c>
+      <c r="D1018" t="s">
         <v>3051</v>
       </c>
-      <c r="D1018" t="s">
+      <c r="E1018" s="2" t="s">
         <v>3052</v>
-      </c>
-      <c r="E1018" s="2" t="s">
-        <v>3053</v>
       </c>
     </row>
     <row r="1019" spans="1:5" x14ac:dyDescent="0.3">
@@ -27150,13 +27389,13 @@
         <v>-0.109375</v>
       </c>
       <c r="C1019" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1019" t="s">
         <v>3054</v>
       </c>
-      <c r="D1019" t="s">
+      <c r="E1019" s="2" t="s">
         <v>3055</v>
-      </c>
-      <c r="E1019" s="2" t="s">
-        <v>3056</v>
       </c>
     </row>
     <row r="1020" spans="1:5" x14ac:dyDescent="0.3">
@@ -27167,13 +27406,13 @@
         <v>-9.375E-2</v>
       </c>
       <c r="C1020" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D1020" t="s">
         <v>3057</v>
       </c>
-      <c r="D1020" t="s">
+      <c r="E1020" s="2" t="s">
         <v>3058</v>
-      </c>
-      <c r="E1020" s="2" t="s">
-        <v>3059</v>
       </c>
     </row>
     <row r="1021" spans="1:5" x14ac:dyDescent="0.3">
@@ -27184,13 +27423,13 @@
         <v>-7.8125E-2</v>
       </c>
       <c r="C1021" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D1021" t="s">
         <v>3060</v>
       </c>
-      <c r="D1021" t="s">
+      <c r="E1021" s="2" t="s">
         <v>3061</v>
-      </c>
-      <c r="E1021" s="2" t="s">
-        <v>3062</v>
       </c>
     </row>
     <row r="1022" spans="1:5" x14ac:dyDescent="0.3">
@@ -27201,13 +27440,13 @@
         <v>-6.25E-2</v>
       </c>
       <c r="C1022" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D1022" t="s">
         <v>3063</v>
       </c>
-      <c r="D1022" t="s">
+      <c r="E1022" s="2" t="s">
         <v>3064</v>
-      </c>
-      <c r="E1022" s="2" t="s">
-        <v>3065</v>
       </c>
     </row>
     <row r="1023" spans="1:5" x14ac:dyDescent="0.3">
@@ -27218,13 +27457,13 @@
         <v>-4.6875E-2</v>
       </c>
       <c r="C1023" t="s">
+        <v>3065</v>
+      </c>
+      <c r="D1023" t="s">
         <v>3066</v>
       </c>
-      <c r="D1023" t="s">
+      <c r="E1023" s="2" t="s">
         <v>3067</v>
-      </c>
-      <c r="E1023" s="2" t="s">
-        <v>3068</v>
       </c>
     </row>
     <row r="1024" spans="1:5" x14ac:dyDescent="0.3">
@@ -27235,13 +27474,13 @@
         <v>-3.125E-2</v>
       </c>
       <c r="C1024" t="s">
+        <v>3068</v>
+      </c>
+      <c r="D1024" t="s">
         <v>3069</v>
       </c>
-      <c r="D1024" t="s">
+      <c r="E1024" s="2" t="s">
         <v>3070</v>
-      </c>
-      <c r="E1024" s="2" t="s">
-        <v>3071</v>
       </c>
     </row>
     <row r="1025" spans="1:6" x14ac:dyDescent="0.3">
@@ -27252,43 +27491,43 @@
         <v>-1.5625E-2</v>
       </c>
       <c r="C1025" t="s">
+        <v>3071</v>
+      </c>
+      <c r="D1025" t="s">
         <v>3072</v>
       </c>
-      <c r="D1025" t="s">
+      <c r="E1025" s="2" t="s">
         <v>3073</v>
       </c>
-      <c r="E1025" s="2" t="s">
-        <v>3074</v>
-      </c>
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1028" s="8" t="s">
-        <v>3090</v>
-      </c>
-      <c r="B1028" s="9"/>
-      <c r="C1028" s="9"/>
-      <c r="D1028" s="9"/>
-      <c r="E1028" s="9"/>
-      <c r="F1028" s="10"/>
+      <c r="A1028" s="10" t="s">
+        <v>3089</v>
+      </c>
+      <c r="B1028" s="11"/>
+      <c r="C1028" s="11"/>
+      <c r="D1028" s="11"/>
+      <c r="E1028" s="11"/>
+      <c r="F1028" s="12"/>
     </row>
     <row r="1029" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1029" t="s">
+        <v>3075</v>
+      </c>
+      <c r="B1029" t="s">
         <v>3076</v>
       </c>
-      <c r="B1029" t="s">
+      <c r="C1029" t="s">
         <v>3077</v>
       </c>
-      <c r="C1029" t="s">
+      <c r="D1029" t="s">
         <v>3078</v>
       </c>
-      <c r="D1029" t="s">
+      <c r="E1029" t="s">
+        <v>3080</v>
+      </c>
+      <c r="F1029" t="s">
         <v>3079</v>
-      </c>
-      <c r="E1029" t="s">
-        <v>3081</v>
-      </c>
-      <c r="F1029" t="s">
-        <v>3080</v>
       </c>
     </row>
     <row r="1030" spans="1:6" x14ac:dyDescent="0.3">
@@ -27315,40 +27554,40 @@
       </c>
     </row>
     <row r="1041" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1041" s="8" t="s">
-        <v>3089</v>
-      </c>
-      <c r="B1041" s="9"/>
-      <c r="C1041" s="9"/>
-      <c r="D1041" s="9"/>
-      <c r="E1041" s="9"/>
-      <c r="F1041" s="9"/>
-      <c r="G1041" s="10"/>
+      <c r="A1041" s="10" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B1041" s="11"/>
+      <c r="C1041" s="11"/>
+      <c r="D1041" s="11"/>
+      <c r="E1041" s="11"/>
+      <c r="F1041" s="11"/>
+      <c r="G1041" s="12"/>
     </row>
     <row r="1042" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B1042" t="s">
         <v>3082</v>
       </c>
-      <c r="B1042" t="s">
+      <c r="C1042" t="s">
         <v>3083</v>
       </c>
-      <c r="C1042" t="s">
+      <c r="D1042" t="s">
         <v>3084</v>
       </c>
-      <c r="D1042" t="s">
+      <c r="E1042" t="s">
         <v>3085</v>
       </c>
-      <c r="E1042" t="s">
+      <c r="F1042" t="s">
         <v>3086</v>
       </c>
-      <c r="F1042" t="s">
+      <c r="G1042" t="s">
         <v>3087</v>
       </c>
-      <c r="G1042" t="s">
-        <v>3088</v>
-      </c>
       <c r="H1042" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="1043" spans="1:8" x14ac:dyDescent="0.3">
@@ -27413,7 +27652,7 @@
         <v>1.2207031250005551E-4</v>
       </c>
       <c r="H1044" s="6">
-        <f t="shared" ref="H1044:H1046" si="0">(F1044-C1044)/C1044</f>
+        <f t="shared" ref="H1044:H1046" si="1">(F1044-C1044)/C1044</f>
         <v>1.2207031250005551E-4</v>
       </c>
     </row>
@@ -27446,7 +27685,7 @@
         <v>2.3282020331068849E-10</v>
       </c>
       <c r="H1045" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.3282020331068849E-10</v>
       </c>
     </row>
@@ -27455,7 +27694,7 @@
         <v>20</v>
       </c>
       <c r="B1046">
-        <f t="shared" ref="B1046:B1047" si="1">2^A1046</f>
+        <f t="shared" ref="B1046" si="2">2^A1046</f>
         <v>1048576</v>
       </c>
       <c r="C1046">
@@ -27463,23 +27702,23 @@
         <v>3.3546262790251185E-4</v>
       </c>
       <c r="D1046">
-        <f t="shared" ref="D1046:D1047" si="2">C1046*B1046</f>
+        <f t="shared" ref="D1046" si="3">C1046*B1046</f>
         <v>351.75806051550427</v>
       </c>
       <c r="E1046" s="7">
-        <f t="shared" ref="E1046:E1047" si="3">ROUND(D1046,0)</f>
+        <f t="shared" ref="E1046" si="4">ROUND(D1046,0)</f>
         <v>352</v>
       </c>
       <c r="F1046">
-        <f t="shared" ref="F1046:F1047" si="4">E1046/B1046</f>
+        <f t="shared" ref="F1046" si="5">E1046/B1046</f>
         <v>3.35693359375E-4</v>
       </c>
       <c r="G1046" s="4">
-        <f t="shared" ref="G1046:G1047" si="5">(F1046-C1046)/C1046</f>
+        <f t="shared" ref="G1046" si="6">(F1046-C1046)/C1046</f>
         <v>6.8780082577543991E-4</v>
       </c>
       <c r="H1046" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.8780082577543991E-4</v>
       </c>
     </row>
@@ -27493,10 +27732,278 @@
         <v>1.5625E-2</v>
       </c>
     </row>
+    <row r="1050" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1050" s="10" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B1050" s="11"/>
+      <c r="C1050" s="11"/>
+      <c r="D1050" s="11"/>
+      <c r="E1050" s="11"/>
+      <c r="F1050" s="11"/>
+      <c r="G1050" s="12"/>
+    </row>
+    <row r="1051" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C1051" t="s">
+        <v>3116</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C1052">
+        <v>976</v>
+      </c>
+      <c r="D1052">
+        <v>6</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1053" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1054" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C1054">
+        <f>D1052*E1054</f>
+        <v>4098</v>
+      </c>
+      <c r="E1054">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1055" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>3102</v>
+      </c>
+      <c r="C1055">
+        <f>C1054+G1055</f>
+        <v>47794</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>3107</v>
+      </c>
+      <c r="F1055" t="s">
+        <v>3108</v>
+      </c>
+      <c r="G1055">
+        <f>2731*16</f>
+        <v>43696</v>
+      </c>
+      <c r="H1055">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1056" t="s">
+        <v>3094</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C1056">
+        <f>C1055*D1052</f>
+        <v>286764</v>
+      </c>
+      <c r="E1056">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1057" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>3104</v>
+      </c>
+      <c r="C1057">
+        <f>C1056+G1057</f>
+        <v>2383916</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>3110</v>
+      </c>
+      <c r="F1057" t="s">
+        <v>3109</v>
+      </c>
+      <c r="G1057">
+        <f>2^21</f>
+        <v>2097152</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1058" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C1058">
+        <f>C1057*D1052</f>
+        <v>14303496</v>
+      </c>
+      <c r="E1058">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1059" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1059">
+        <f>C1058+G1059</f>
+        <v>81412360</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>3111</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>3112</v>
+      </c>
+      <c r="G1059">
+        <f>2^26</f>
+        <v>67108864</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1060" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C1060">
+        <f>C1059*D1052</f>
+        <v>488474160</v>
+      </c>
+      <c r="E1060">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1061" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1061">
+        <f>C1060+G1061</f>
+        <v>1562215984</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>3113</v>
+      </c>
+      <c r="F1061" t="s">
+        <v>3114</v>
+      </c>
+      <c r="G1061">
+        <f>2^30</f>
+        <v>1073741824</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1062" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>3106</v>
+      </c>
+      <c r="C1062" s="2">
+        <f>C1061*495312</f>
+        <v>773784323467008</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>3115</v>
+      </c>
+      <c r="G1062" s="2">
+        <f>495312*2^30</f>
+        <v>531837210329088</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1063" t="s">
+        <v>3119</v>
+      </c>
+      <c r="G1063" s="2">
+        <v>531837457726680</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1064" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C1064" s="2">
+        <f>C1062-E978</f>
+        <v>241946865740328</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1065" t="s">
+        <v>3079</v>
+      </c>
+      <c r="C1065">
+        <f>(C1062-E984)/E984</f>
+        <v>0.32472550354327395</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D1066" s="2"/>
+    </row>
+    <row r="1068" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C1068" s="9">
+        <v>531837457726680</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1072">
+        <v>-0.75</v>
+      </c>
+      <c r="B1072">
+        <f>EXP(A1072)</f>
+        <v>0.47236655274101469</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1073">
+        <v>-0.65625</v>
+      </c>
+      <c r="B1073">
+        <f>EXP(A1073)</f>
+        <v>0.51879316565388933</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>3123</v>
+      </c>
+      <c r="E1073">
+        <f>B1072+B1072*(A1073-A1072)+B1072/2*(A1073-A1072)^2+B1072/6*(A1073-A1072)^3+B1072/24*(A1073-A1072)^4</f>
+        <v>0.5187931366952474</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1041:G1041"/>
     <mergeCell ref="A1028:F1028"/>
+    <mergeCell ref="A1050:G1050"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8b65b6adf7979/桌面/Github File/IC_Design_Laboratory/HW5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="11_1B85D0BDD370594FA3B82111595ED87656CB84C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B55C661F-0CC7-4A37-923C-6625925A433E}"/>
+  <xr:revisionPtr revIDLastSave="503" documentId="11_1B85D0BDD370594FA3B82111595ED87656CB84C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E8EEAA7-F43D-4855-879D-B5987E5E595E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="3125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="3137">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -9458,6 +9458,54 @@
   </si>
   <si>
     <t>DATAFLOW設計: 這部分錯誤, 因為對其不是左移四位, 應為六位, 直接更新在code上</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除法誤差來源計算</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp_sum</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp_shift_9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>softmax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>14-bit integer + 20-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20-bit integer + 20-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/2^6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;表示1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除法器輸出值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9473,7 +9521,7 @@
     <numFmt numFmtId="180" formatCode="0.0000000"/>
     <numFmt numFmtId="181" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9501,6 +9549,12 @@
       <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -9593,7 +9647,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -9615,6 +9669,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -9922,8 +9978,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1073"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H1087"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.8984375" bestFit="1" customWidth="1"/>
@@ -9936,7 +9992,7 @@
     <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9956,7 +10012,7 @@
         <v>3091</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -9980,7 +10036,7 @@
         <v>-412572841297000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -10001,7 +10057,7 @@
         <v>1556203091770350</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>2</v>
       </c>
@@ -10022,7 +10078,7 @@
         <v>-394563285381620</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -10043,7 +10099,7 @@
         <v>1574496256924050</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -10064,7 +10120,7 @@
         <v>-375982044793950</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -10085,7 +10141,7 @@
         <v>1593370109473680</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -10106,7 +10162,7 @@
         <v>-356810972314470</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -10127,7 +10183,7 @@
         <v>1612843082415870</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -10148,7 +10204,7 @@
         <v>-337031344669070</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
@@ -10169,7 +10225,7 @@
         <v>1632934193873380</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>10</v>
       </c>
@@ -10190,7 +10246,7 @@
         <v>-316623844243150</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>11</v>
       </c>
@@ -10211,7 +10267,7 @@
         <v>1653663065669000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>12</v>
       </c>
@@ -10232,7 +10288,7 @@
         <v>-295568540215170</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>13</v>
       </c>
@@ -10253,7 +10309,7 @@
         <v>1675049942489020</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>14</v>
       </c>
@@ -10274,7 +10330,7 @@
         <v>-273844869091410</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>15</v>
       </c>
@@ -10295,7 +10351,7 @@
         <v>1697115711655080</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>16</v>
       </c>
@@ -10316,7 +10372,7 @@
         <v>-251431614622790</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -10337,7 +10393,7 @@
         <v>1719881923523550</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -10358,7 +10414,7 @@
         <v>-228306887084200</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
@@ -10379,7 +10435,7 @@
         <v>1743370812532580</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>20</v>
       </c>
@@ -10400,7 +10456,7 @@
         <v>-204448101896040</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>21</v>
       </c>
@@ -10421,7 +10477,7 @@
         <v>1767605318917110</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>22</v>
       </c>
@@ -10438,7 +10494,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>23</v>
       </c>
@@ -10455,7 +10511,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>24</v>
       </c>
@@ -10472,7 +10528,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>25</v>
       </c>
@@ -10489,7 +10545,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>26</v>
       </c>
@@ -10506,7 +10562,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>27</v>
       </c>
@@ -10523,7 +10579,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>28</v>
       </c>
@@ -10540,7 +10596,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>29</v>
       </c>
@@ -10557,7 +10613,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>30</v>
       </c>
@@ -10574,7 +10630,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>31</v>
       </c>
@@ -10591,7 +10647,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -10608,7 +10664,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>33</v>
       </c>
@@ -10625,7 +10681,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>34</v>
       </c>
@@ -10642,7 +10698,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -10659,7 +10715,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -10676,7 +10732,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>37</v>
       </c>
@@ -10693,7 +10749,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>38</v>
       </c>
@@ -10710,7 +10766,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>39</v>
       </c>
@@ -10727,7 +10783,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -10744,7 +10800,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>41</v>
       </c>
@@ -10761,7 +10817,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -10778,7 +10834,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -10795,7 +10851,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -10812,7 +10868,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -10829,7 +10885,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -10846,7 +10902,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -10863,7 +10919,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -10880,7 +10936,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>49</v>
       </c>
@@ -10897,7 +10953,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>50</v>
       </c>
@@ -10914,7 +10970,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>51</v>
       </c>
@@ -10931,7 +10987,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>52</v>
       </c>
@@ -10948,7 +11004,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>53</v>
       </c>
@@ -10965,7 +11021,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -10982,7 +11038,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>55</v>
       </c>
@@ -10999,7 +11055,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>56</v>
       </c>
@@ -11016,7 +11072,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>57</v>
       </c>
@@ -11033,7 +11089,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>58</v>
       </c>
@@ -11050,7 +11106,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>59</v>
       </c>
@@ -11067,7 +11123,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>60</v>
       </c>
@@ -11084,7 +11140,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>61</v>
       </c>
@@ -11101,7 +11157,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>62</v>
       </c>
@@ -11118,7 +11174,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>63</v>
       </c>
@@ -11135,7 +11191,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>64</v>
       </c>
@@ -11155,7 +11211,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>65</v>
       </c>
@@ -11172,7 +11228,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>66</v>
       </c>
@@ -11189,7 +11245,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>67</v>
       </c>
@@ -11206,7 +11262,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>68</v>
       </c>
@@ -11223,7 +11279,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>69</v>
       </c>
@@ -11240,7 +11296,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>70</v>
       </c>
@@ -11257,7 +11313,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>71</v>
       </c>
@@ -11274,7 +11330,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>72</v>
       </c>
@@ -11291,7 +11347,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75">
         <v>73</v>
       </c>
@@ -11308,7 +11364,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76">
         <v>74</v>
       </c>
@@ -11325,7 +11381,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77">
         <v>75</v>
       </c>
@@ -11342,7 +11398,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>76</v>
       </c>
@@ -11359,7 +11415,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>77</v>
       </c>
@@ -11376,7 +11432,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80">
         <v>78</v>
       </c>
@@ -11393,7 +11449,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>79</v>
       </c>
@@ -11410,7 +11466,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>80</v>
       </c>
@@ -11427,7 +11483,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5">
       <c r="A83">
         <v>81</v>
       </c>
@@ -11444,7 +11500,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>82</v>
       </c>
@@ -11461,7 +11517,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>83</v>
       </c>
@@ -11478,7 +11534,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>84</v>
       </c>
@@ -11495,7 +11551,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>85</v>
       </c>
@@ -11512,7 +11568,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>86</v>
       </c>
@@ -11529,7 +11585,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5">
       <c r="A89">
         <v>87</v>
       </c>
@@ -11546,7 +11602,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>88</v>
       </c>
@@ -11563,7 +11619,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>89</v>
       </c>
@@ -11580,7 +11636,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>90</v>
       </c>
@@ -11597,7 +11653,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>91</v>
       </c>
@@ -11614,7 +11670,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>92</v>
       </c>
@@ -11631,7 +11687,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>93</v>
       </c>
@@ -11648,7 +11704,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5">
       <c r="A96">
         <v>94</v>
       </c>
@@ -11665,7 +11721,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>95</v>
       </c>
@@ -11682,7 +11738,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>96</v>
       </c>
@@ -11699,7 +11755,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5">
       <c r="A99">
         <v>97</v>
       </c>
@@ -11716,7 +11772,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5">
       <c r="A100">
         <v>98</v>
       </c>
@@ -11733,7 +11789,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5">
       <c r="A101">
         <v>99</v>
       </c>
@@ -11750,7 +11806,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>100</v>
       </c>
@@ -11767,7 +11823,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5">
       <c r="A103">
         <v>101</v>
       </c>
@@ -11784,7 +11840,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5">
       <c r="A104">
         <v>102</v>
       </c>
@@ -11801,7 +11857,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105">
         <v>103</v>
       </c>
@@ -11818,7 +11874,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106">
         <v>104</v>
       </c>
@@ -11835,7 +11891,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107">
         <v>105</v>
       </c>
@@ -11852,7 +11908,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108">
         <v>106</v>
       </c>
@@ -11869,7 +11925,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5">
       <c r="A109">
         <v>107</v>
       </c>
@@ -11886,7 +11942,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110">
         <v>108</v>
       </c>
@@ -11903,7 +11959,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5">
       <c r="A111">
         <v>109</v>
       </c>
@@ -11920,7 +11976,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5">
       <c r="A112">
         <v>110</v>
       </c>
@@ -11937,7 +11993,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5">
       <c r="A113">
         <v>111</v>
       </c>
@@ -11954,7 +12010,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5">
       <c r="A114">
         <v>112</v>
       </c>
@@ -11971,7 +12027,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5">
       <c r="A115">
         <v>113</v>
       </c>
@@ -11988,7 +12044,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5">
       <c r="A116">
         <v>114</v>
       </c>
@@ -12005,7 +12061,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5">
       <c r="A117">
         <v>115</v>
       </c>
@@ -12022,7 +12078,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5">
       <c r="A118">
         <v>116</v>
       </c>
@@ -12039,7 +12095,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5">
       <c r="A119">
         <v>117</v>
       </c>
@@ -12056,7 +12112,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5">
       <c r="A120">
         <v>118</v>
       </c>
@@ -12073,7 +12129,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5">
       <c r="A121">
         <v>119</v>
       </c>
@@ -12090,7 +12146,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5">
       <c r="A122">
         <v>120</v>
       </c>
@@ -12107,7 +12163,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5">
       <c r="A123">
         <v>121</v>
       </c>
@@ -12124,7 +12180,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5">
       <c r="A124">
         <v>122</v>
       </c>
@@ -12141,7 +12197,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5">
       <c r="A125">
         <v>123</v>
       </c>
@@ -12158,7 +12214,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5">
       <c r="A126">
         <v>124</v>
       </c>
@@ -12175,7 +12231,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5">
       <c r="A127">
         <v>125</v>
       </c>
@@ -12192,7 +12248,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5">
       <c r="A128">
         <v>126</v>
       </c>
@@ -12209,7 +12265,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6">
       <c r="A129">
         <v>127</v>
       </c>
@@ -12226,7 +12282,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6">
       <c r="A130">
         <v>128</v>
       </c>
@@ -12246,7 +12302,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6">
       <c r="A131">
         <v>129</v>
       </c>
@@ -12263,7 +12319,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6">
       <c r="A132">
         <v>130</v>
       </c>
@@ -12280,7 +12336,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6">
       <c r="A133">
         <v>131</v>
       </c>
@@ -12297,7 +12353,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6">
       <c r="A134">
         <v>132</v>
       </c>
@@ -12314,7 +12370,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6">
       <c r="A135">
         <v>133</v>
       </c>
@@ -12331,7 +12387,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6">
       <c r="A136">
         <v>134</v>
       </c>
@@ -12348,7 +12404,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6">
       <c r="A137">
         <v>135</v>
       </c>
@@ -12365,7 +12421,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6">
       <c r="A138">
         <v>136</v>
       </c>
@@ -12382,7 +12438,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6">
       <c r="A139">
         <v>137</v>
       </c>
@@ -12399,7 +12455,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6">
       <c r="A140">
         <v>138</v>
       </c>
@@ -12416,7 +12472,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6">
       <c r="A141">
         <v>139</v>
       </c>
@@ -12433,7 +12489,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6">
       <c r="A142">
         <v>140</v>
       </c>
@@ -12450,7 +12506,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6">
       <c r="A143">
         <v>141</v>
       </c>
@@ -12467,7 +12523,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6">
       <c r="A144">
         <v>142</v>
       </c>
@@ -12484,7 +12540,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5">
       <c r="A145">
         <v>143</v>
       </c>
@@ -12501,7 +12557,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5">
       <c r="A146">
         <v>144</v>
       </c>
@@ -12518,7 +12574,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5">
       <c r="A147">
         <v>145</v>
       </c>
@@ -12535,7 +12591,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5">
       <c r="A148">
         <v>146</v>
       </c>
@@ -12552,7 +12608,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5">
       <c r="A149">
         <v>147</v>
       </c>
@@ -12569,7 +12625,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5">
       <c r="A150">
         <v>148</v>
       </c>
@@ -12586,7 +12642,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5">
       <c r="A151">
         <v>149</v>
       </c>
@@ -12603,7 +12659,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5">
       <c r="A152">
         <v>150</v>
       </c>
@@ -12620,7 +12676,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5">
       <c r="A153">
         <v>151</v>
       </c>
@@ -12637,7 +12693,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5">
       <c r="A154">
         <v>152</v>
       </c>
@@ -12654,7 +12710,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5">
       <c r="A155">
         <v>153</v>
       </c>
@@ -12671,7 +12727,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5">
       <c r="A156">
         <v>154</v>
       </c>
@@ -12688,7 +12744,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5">
       <c r="A157">
         <v>155</v>
       </c>
@@ -12705,7 +12761,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5">
       <c r="A158">
         <v>156</v>
       </c>
@@ -12722,7 +12778,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5">
       <c r="A159">
         <v>157</v>
       </c>
@@ -12739,7 +12795,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5">
       <c r="A160">
         <v>158</v>
       </c>
@@ -12756,7 +12812,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5">
       <c r="A161">
         <v>159</v>
       </c>
@@ -12773,7 +12829,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5">
       <c r="A162">
         <v>160</v>
       </c>
@@ -12790,7 +12846,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5">
       <c r="A163">
         <v>161</v>
       </c>
@@ -12807,7 +12863,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5">
       <c r="A164">
         <v>162</v>
       </c>
@@ -12824,7 +12880,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5">
       <c r="A165">
         <v>163</v>
       </c>
@@ -12841,7 +12897,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5">
       <c r="A166">
         <v>164</v>
       </c>
@@ -12858,7 +12914,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5">
       <c r="A167">
         <v>165</v>
       </c>
@@ -12875,7 +12931,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5">
       <c r="A168">
         <v>166</v>
       </c>
@@ -12892,7 +12948,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5">
       <c r="A169">
         <v>167</v>
       </c>
@@ -12909,7 +12965,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5">
       <c r="A170">
         <v>168</v>
       </c>
@@ -12926,7 +12982,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5">
       <c r="A171">
         <v>169</v>
       </c>
@@ -12943,7 +12999,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5">
       <c r="A172">
         <v>170</v>
       </c>
@@ -12960,7 +13016,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5">
       <c r="A173">
         <v>171</v>
       </c>
@@ -12977,7 +13033,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5">
       <c r="A174">
         <v>172</v>
       </c>
@@ -12994,7 +13050,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5">
       <c r="A175">
         <v>173</v>
       </c>
@@ -13011,7 +13067,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5">
       <c r="A176">
         <v>174</v>
       </c>
@@ -13028,7 +13084,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5">
       <c r="A177">
         <v>175</v>
       </c>
@@ -13045,7 +13101,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5">
       <c r="A178">
         <v>176</v>
       </c>
@@ -13062,7 +13118,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5">
       <c r="A179">
         <v>177</v>
       </c>
@@ -13079,7 +13135,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5">
       <c r="A180">
         <v>178</v>
       </c>
@@ -13096,7 +13152,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5">
       <c r="A181">
         <v>179</v>
       </c>
@@ -13113,7 +13169,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5">
       <c r="A182">
         <v>180</v>
       </c>
@@ -13130,7 +13186,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5">
       <c r="A183">
         <v>181</v>
       </c>
@@ -13147,7 +13203,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5">
       <c r="A184">
         <v>182</v>
       </c>
@@ -13164,7 +13220,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5">
       <c r="A185">
         <v>183</v>
       </c>
@@ -13181,7 +13237,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5">
       <c r="A186">
         <v>184</v>
       </c>
@@ -13198,7 +13254,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5">
       <c r="A187">
         <v>185</v>
       </c>
@@ -13215,7 +13271,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5">
       <c r="A188">
         <v>186</v>
       </c>
@@ -13232,7 +13288,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5">
       <c r="A189">
         <v>187</v>
       </c>
@@ -13249,7 +13305,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5">
       <c r="A190">
         <v>188</v>
       </c>
@@ -13266,7 +13322,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5">
       <c r="A191">
         <v>189</v>
       </c>
@@ -13283,7 +13339,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5">
       <c r="A192">
         <v>190</v>
       </c>
@@ -13300,7 +13356,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6">
       <c r="A193">
         <v>191</v>
       </c>
@@ -13317,7 +13373,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6">
       <c r="A194">
         <v>192</v>
       </c>
@@ -13337,7 +13393,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6">
       <c r="A195">
         <v>193</v>
       </c>
@@ -13354,7 +13410,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6">
       <c r="A196">
         <v>194</v>
       </c>
@@ -13371,7 +13427,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6">
       <c r="A197">
         <v>195</v>
       </c>
@@ -13388,7 +13444,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6">
       <c r="A198">
         <v>196</v>
       </c>
@@ -13405,7 +13461,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6">
       <c r="A199">
         <v>197</v>
       </c>
@@ -13422,7 +13478,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6">
       <c r="A200">
         <v>198</v>
       </c>
@@ -13439,7 +13495,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6">
       <c r="A201">
         <v>199</v>
       </c>
@@ -13456,7 +13512,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6">
       <c r="A202">
         <v>200</v>
       </c>
@@ -13473,7 +13529,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6">
       <c r="A203">
         <v>201</v>
       </c>
@@ -13490,7 +13546,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6">
       <c r="A204">
         <v>202</v>
       </c>
@@ -13507,7 +13563,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6">
       <c r="A205">
         <v>203</v>
       </c>
@@ -13524,7 +13580,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6">
       <c r="A206">
         <v>204</v>
       </c>
@@ -13541,7 +13597,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6">
       <c r="A207">
         <v>205</v>
       </c>
@@ -13558,7 +13614,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6">
       <c r="A208">
         <v>206</v>
       </c>
@@ -13575,7 +13631,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5">
       <c r="A209">
         <v>207</v>
       </c>
@@ -13592,7 +13648,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5">
       <c r="A210">
         <v>208</v>
       </c>
@@ -13609,7 +13665,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5">
       <c r="A211">
         <v>209</v>
       </c>
@@ -13626,7 +13682,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5">
       <c r="A212">
         <v>210</v>
       </c>
@@ -13643,7 +13699,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5">
       <c r="A213">
         <v>211</v>
       </c>
@@ -13660,7 +13716,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5">
       <c r="A214">
         <v>212</v>
       </c>
@@ -13677,7 +13733,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5">
       <c r="A215">
         <v>213</v>
       </c>
@@ -13694,7 +13750,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5">
       <c r="A216">
         <v>214</v>
       </c>
@@ -13711,7 +13767,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5">
       <c r="A217">
         <v>215</v>
       </c>
@@ -13728,7 +13784,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5">
       <c r="A218">
         <v>216</v>
       </c>
@@ -13745,7 +13801,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5">
       <c r="A219">
         <v>217</v>
       </c>
@@ -13762,7 +13818,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5">
       <c r="A220">
         <v>218</v>
       </c>
@@ -13779,7 +13835,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5">
       <c r="A221">
         <v>219</v>
       </c>
@@ -13796,7 +13852,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5">
       <c r="A222">
         <v>220</v>
       </c>
@@ -13813,7 +13869,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5">
       <c r="A223">
         <v>221</v>
       </c>
@@ -13830,7 +13886,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5">
       <c r="A224">
         <v>222</v>
       </c>
@@ -13847,7 +13903,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5">
       <c r="A225">
         <v>223</v>
       </c>
@@ -13864,7 +13920,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5">
       <c r="A226">
         <v>224</v>
       </c>
@@ -13881,7 +13937,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5">
       <c r="A227">
         <v>225</v>
       </c>
@@ -13898,7 +13954,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5">
       <c r="A228">
         <v>226</v>
       </c>
@@ -13915,7 +13971,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5">
       <c r="A229">
         <v>227</v>
       </c>
@@ -13932,7 +13988,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5">
       <c r="A230">
         <v>228</v>
       </c>
@@ -13949,7 +14005,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5">
       <c r="A231">
         <v>229</v>
       </c>
@@ -13966,7 +14022,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5">
       <c r="A232">
         <v>230</v>
       </c>
@@ -13983,7 +14039,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5">
       <c r="A233">
         <v>231</v>
       </c>
@@ -14000,7 +14056,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5">
       <c r="A234">
         <v>232</v>
       </c>
@@ -14017,7 +14073,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5">
       <c r="A235">
         <v>233</v>
       </c>
@@ -14034,7 +14090,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5">
       <c r="A236">
         <v>234</v>
       </c>
@@ -14051,7 +14107,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5">
       <c r="A237">
         <v>235</v>
       </c>
@@ -14068,7 +14124,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5">
       <c r="A238">
         <v>236</v>
       </c>
@@ -14085,7 +14141,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5">
       <c r="A239">
         <v>237</v>
       </c>
@@ -14102,7 +14158,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5">
       <c r="A240">
         <v>238</v>
       </c>
@@ -14119,7 +14175,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5">
       <c r="A241">
         <v>239</v>
       </c>
@@ -14136,7 +14192,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5">
       <c r="A242">
         <v>240</v>
       </c>
@@ -14153,7 +14209,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5">
       <c r="A243">
         <v>241</v>
       </c>
@@ -14170,7 +14226,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5">
       <c r="A244">
         <v>242</v>
       </c>
@@ -14187,7 +14243,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5">
       <c r="A245">
         <v>243</v>
       </c>
@@ -14204,7 +14260,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5">
       <c r="A246">
         <v>244</v>
       </c>
@@ -14221,7 +14277,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5">
       <c r="A247">
         <v>245</v>
       </c>
@@ -14238,7 +14294,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5">
       <c r="A248">
         <v>246</v>
       </c>
@@ -14255,7 +14311,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5">
       <c r="A249">
         <v>247</v>
       </c>
@@ -14272,7 +14328,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5">
       <c r="A250">
         <v>248</v>
       </c>
@@ -14289,7 +14345,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5">
       <c r="A251">
         <v>249</v>
       </c>
@@ -14306,7 +14362,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5">
       <c r="A252">
         <v>250</v>
       </c>
@@ -14323,7 +14379,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5">
       <c r="A253">
         <v>251</v>
       </c>
@@ -14340,7 +14396,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5">
       <c r="A254">
         <v>252</v>
       </c>
@@ -14357,7 +14413,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5">
       <c r="A255">
         <v>253</v>
       </c>
@@ -14374,7 +14430,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5">
       <c r="A256">
         <v>254</v>
       </c>
@@ -14391,7 +14447,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6">
       <c r="A257">
         <v>255</v>
       </c>
@@ -14408,7 +14464,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6">
       <c r="A258">
         <v>256</v>
       </c>
@@ -14428,7 +14484,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6">
       <c r="A259">
         <v>257</v>
       </c>
@@ -14445,7 +14501,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6">
       <c r="A260">
         <v>258</v>
       </c>
@@ -14462,7 +14518,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6">
       <c r="A261">
         <v>259</v>
       </c>
@@ -14479,7 +14535,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6">
       <c r="A262">
         <v>260</v>
       </c>
@@ -14496,7 +14552,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6">
       <c r="A263">
         <v>261</v>
       </c>
@@ -14513,7 +14569,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6">
       <c r="A264">
         <v>262</v>
       </c>
@@ -14530,7 +14586,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6">
       <c r="A265">
         <v>263</v>
       </c>
@@ -14547,7 +14603,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6">
       <c r="A266">
         <v>264</v>
       </c>
@@ -14564,7 +14620,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6">
       <c r="A267">
         <v>265</v>
       </c>
@@ -14581,7 +14637,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6">
       <c r="A268">
         <v>266</v>
       </c>
@@ -14598,7 +14654,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6">
       <c r="A269">
         <v>267</v>
       </c>
@@ -14615,7 +14671,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6">
       <c r="A270">
         <v>268</v>
       </c>
@@ -14632,7 +14688,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6">
       <c r="A271">
         <v>269</v>
       </c>
@@ -14649,7 +14705,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6">
       <c r="A272">
         <v>270</v>
       </c>
@@ -14666,7 +14722,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5">
       <c r="A273">
         <v>271</v>
       </c>
@@ -14683,7 +14739,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5">
       <c r="A274">
         <v>272</v>
       </c>
@@ -14700,7 +14756,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5">
       <c r="A275">
         <v>273</v>
       </c>
@@ -14717,7 +14773,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5">
       <c r="A276">
         <v>274</v>
       </c>
@@ -14734,7 +14790,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5">
       <c r="A277">
         <v>275</v>
       </c>
@@ -14751,7 +14807,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5">
       <c r="A278">
         <v>276</v>
       </c>
@@ -14768,7 +14824,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5">
       <c r="A279">
         <v>277</v>
       </c>
@@ -14785,7 +14841,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5">
       <c r="A280">
         <v>278</v>
       </c>
@@ -14802,7 +14858,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5">
       <c r="A281">
         <v>279</v>
       </c>
@@ -14819,7 +14875,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5">
       <c r="A282">
         <v>280</v>
       </c>
@@ -14836,7 +14892,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5">
       <c r="A283">
         <v>281</v>
       </c>
@@ -14853,7 +14909,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5">
       <c r="A284">
         <v>282</v>
       </c>
@@ -14870,7 +14926,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5">
       <c r="A285">
         <v>283</v>
       </c>
@@ -14887,7 +14943,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5">
       <c r="A286">
         <v>284</v>
       </c>
@@ -14904,7 +14960,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5">
       <c r="A287">
         <v>285</v>
       </c>
@@ -14921,7 +14977,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5">
       <c r="A288">
         <v>286</v>
       </c>
@@ -14938,7 +14994,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5">
       <c r="A289">
         <v>287</v>
       </c>
@@ -14955,7 +15011,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5">
       <c r="A290">
         <v>288</v>
       </c>
@@ -14972,7 +15028,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5">
       <c r="A291">
         <v>289</v>
       </c>
@@ -14989,7 +15045,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5">
       <c r="A292">
         <v>290</v>
       </c>
@@ -15006,7 +15062,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5">
       <c r="A293">
         <v>291</v>
       </c>
@@ -15023,7 +15079,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5">
       <c r="A294">
         <v>292</v>
       </c>
@@ -15040,7 +15096,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5">
       <c r="A295">
         <v>293</v>
       </c>
@@ -15057,7 +15113,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5">
       <c r="A296">
         <v>294</v>
       </c>
@@ -15074,7 +15130,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5">
       <c r="A297">
         <v>295</v>
       </c>
@@ -15091,7 +15147,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5">
       <c r="A298">
         <v>296</v>
       </c>
@@ -15108,7 +15164,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5">
       <c r="A299">
         <v>297</v>
       </c>
@@ -15125,7 +15181,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5">
       <c r="A300">
         <v>298</v>
       </c>
@@ -15142,7 +15198,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5">
       <c r="A301">
         <v>299</v>
       </c>
@@ -15159,7 +15215,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5">
       <c r="A302">
         <v>300</v>
       </c>
@@ -15176,7 +15232,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5">
       <c r="A303">
         <v>301</v>
       </c>
@@ -15193,7 +15249,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5">
       <c r="A304">
         <v>302</v>
       </c>
@@ -15210,7 +15266,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5">
       <c r="A305">
         <v>303</v>
       </c>
@@ -15227,7 +15283,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5">
       <c r="A306">
         <v>304</v>
       </c>
@@ -15244,7 +15300,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5">
       <c r="A307">
         <v>305</v>
       </c>
@@ -15261,7 +15317,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5">
       <c r="A308">
         <v>306</v>
       </c>
@@ -15278,7 +15334,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5">
       <c r="A309">
         <v>307</v>
       </c>
@@ -15295,7 +15351,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5">
       <c r="A310">
         <v>308</v>
       </c>
@@ -15312,7 +15368,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5">
       <c r="A311">
         <v>309</v>
       </c>
@@ -15329,7 +15385,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5">
       <c r="A312">
         <v>310</v>
       </c>
@@ -15346,7 +15402,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5">
       <c r="A313">
         <v>311</v>
       </c>
@@ -15363,7 +15419,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5">
       <c r="A314">
         <v>312</v>
       </c>
@@ -15380,7 +15436,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5">
       <c r="A315">
         <v>313</v>
       </c>
@@ -15397,7 +15453,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5">
       <c r="A316">
         <v>314</v>
       </c>
@@ -15414,7 +15470,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5">
       <c r="A317">
         <v>315</v>
       </c>
@@ -15431,7 +15487,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5">
       <c r="A318">
         <v>316</v>
       </c>
@@ -15448,7 +15504,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5">
       <c r="A319">
         <v>317</v>
       </c>
@@ -15465,7 +15521,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5">
       <c r="A320">
         <v>318</v>
       </c>
@@ -15482,7 +15538,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6">
       <c r="A321">
         <v>319</v>
       </c>
@@ -15499,7 +15555,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6">
       <c r="A322">
         <v>320</v>
       </c>
@@ -15519,7 +15575,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6">
       <c r="A323">
         <v>321</v>
       </c>
@@ -15536,7 +15592,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6">
       <c r="A324">
         <v>322</v>
       </c>
@@ -15553,7 +15609,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6">
       <c r="A325">
         <v>323</v>
       </c>
@@ -15570,7 +15626,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6">
       <c r="A326">
         <v>324</v>
       </c>
@@ -15587,7 +15643,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6">
       <c r="A327">
         <v>325</v>
       </c>
@@ -15604,7 +15660,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6">
       <c r="A328">
         <v>326</v>
       </c>
@@ -15621,7 +15677,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6">
       <c r="A329">
         <v>327</v>
       </c>
@@ -15638,7 +15694,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6">
       <c r="A330">
         <v>328</v>
       </c>
@@ -15655,7 +15711,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6">
       <c r="A331">
         <v>329</v>
       </c>
@@ -15672,7 +15728,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6">
       <c r="A332">
         <v>330</v>
       </c>
@@ -15689,7 +15745,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6">
       <c r="A333">
         <v>331</v>
       </c>
@@ -15706,7 +15762,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6">
       <c r="A334">
         <v>332</v>
       </c>
@@ -15723,7 +15779,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6">
       <c r="A335">
         <v>333</v>
       </c>
@@ -15740,7 +15796,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6">
       <c r="A336">
         <v>334</v>
       </c>
@@ -15757,7 +15813,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5">
       <c r="A337">
         <v>335</v>
       </c>
@@ -15774,7 +15830,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5">
       <c r="A338">
         <v>336</v>
       </c>
@@ -15791,7 +15847,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5">
       <c r="A339">
         <v>337</v>
       </c>
@@ -15808,7 +15864,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5">
       <c r="A340">
         <v>338</v>
       </c>
@@ -15825,7 +15881,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5">
       <c r="A341">
         <v>339</v>
       </c>
@@ -15842,7 +15898,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5">
       <c r="A342">
         <v>340</v>
       </c>
@@ -15859,7 +15915,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5">
       <c r="A343">
         <v>341</v>
       </c>
@@ -15876,7 +15932,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5">
       <c r="A344">
         <v>342</v>
       </c>
@@ -15893,7 +15949,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5">
       <c r="A345">
         <v>343</v>
       </c>
@@ -15910,7 +15966,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5">
       <c r="A346">
         <v>344</v>
       </c>
@@ -15927,7 +15983,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5">
       <c r="A347">
         <v>345</v>
       </c>
@@ -15944,7 +16000,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5">
       <c r="A348">
         <v>346</v>
       </c>
@@ -15961,7 +16017,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5">
       <c r="A349">
         <v>347</v>
       </c>
@@ -15978,7 +16034,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5">
       <c r="A350">
         <v>348</v>
       </c>
@@ -15995,7 +16051,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5">
       <c r="A351">
         <v>349</v>
       </c>
@@ -16012,7 +16068,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5">
       <c r="A352">
         <v>350</v>
       </c>
@@ -16029,7 +16085,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5">
       <c r="A353">
         <v>351</v>
       </c>
@@ -16046,7 +16102,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5">
       <c r="A354">
         <v>352</v>
       </c>
@@ -16063,7 +16119,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5">
       <c r="A355">
         <v>353</v>
       </c>
@@ -16080,7 +16136,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5">
       <c r="A356">
         <v>354</v>
       </c>
@@ -16097,7 +16153,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5">
       <c r="A357">
         <v>355</v>
       </c>
@@ -16114,7 +16170,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5">
       <c r="A358">
         <v>356</v>
       </c>
@@ -16131,7 +16187,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5">
       <c r="A359">
         <v>357</v>
       </c>
@@ -16148,7 +16204,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5">
       <c r="A360">
         <v>358</v>
       </c>
@@ -16165,7 +16221,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5">
       <c r="A361">
         <v>359</v>
       </c>
@@ -16182,7 +16238,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5">
       <c r="A362">
         <v>360</v>
       </c>
@@ -16199,7 +16255,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5">
       <c r="A363">
         <v>361</v>
       </c>
@@ -16216,7 +16272,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5">
       <c r="A364">
         <v>362</v>
       </c>
@@ -16233,7 +16289,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5">
       <c r="A365">
         <v>363</v>
       </c>
@@ -16250,7 +16306,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5">
       <c r="A366">
         <v>364</v>
       </c>
@@ -16267,7 +16323,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5">
       <c r="A367">
         <v>365</v>
       </c>
@@ -16284,7 +16340,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5">
       <c r="A368">
         <v>366</v>
       </c>
@@ -16301,7 +16357,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5">
       <c r="A369">
         <v>367</v>
       </c>
@@ -16318,7 +16374,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5">
       <c r="A370">
         <v>368</v>
       </c>
@@ -16335,7 +16391,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5">
       <c r="A371">
         <v>369</v>
       </c>
@@ -16352,7 +16408,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5">
       <c r="A372">
         <v>370</v>
       </c>
@@ -16369,7 +16425,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5">
       <c r="A373">
         <v>371</v>
       </c>
@@ -16386,7 +16442,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5">
       <c r="A374">
         <v>372</v>
       </c>
@@ -16403,7 +16459,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5">
       <c r="A375">
         <v>373</v>
       </c>
@@ -16420,7 +16476,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5">
       <c r="A376">
         <v>374</v>
       </c>
@@ -16437,7 +16493,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5">
       <c r="A377">
         <v>375</v>
       </c>
@@ -16454,7 +16510,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5">
       <c r="A378">
         <v>376</v>
       </c>
@@ -16471,7 +16527,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5">
       <c r="A379">
         <v>377</v>
       </c>
@@ -16488,7 +16544,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5">
       <c r="A380">
         <v>378</v>
       </c>
@@ -16505,7 +16561,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5">
       <c r="A381">
         <v>379</v>
       </c>
@@ -16522,7 +16578,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5">
       <c r="A382">
         <v>380</v>
       </c>
@@ -16539,7 +16595,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5">
       <c r="A383">
         <v>381</v>
       </c>
@@ -16556,7 +16612,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5">
       <c r="A384">
         <v>382</v>
       </c>
@@ -16573,7 +16629,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6">
       <c r="A385">
         <v>383</v>
       </c>
@@ -16590,7 +16646,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6">
       <c r="A386">
         <v>384</v>
       </c>
@@ -16610,7 +16666,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6">
       <c r="A387">
         <v>385</v>
       </c>
@@ -16627,7 +16683,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6">
       <c r="A388">
         <v>386</v>
       </c>
@@ -16644,7 +16700,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6">
       <c r="A389">
         <v>387</v>
       </c>
@@ -16661,7 +16717,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6">
       <c r="A390">
         <v>388</v>
       </c>
@@ -16678,7 +16734,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6">
       <c r="A391">
         <v>389</v>
       </c>
@@ -16695,7 +16751,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6">
       <c r="A392">
         <v>390</v>
       </c>
@@ -16712,7 +16768,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6">
       <c r="A393">
         <v>391</v>
       </c>
@@ -16729,7 +16785,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6">
       <c r="A394">
         <v>392</v>
       </c>
@@ -16746,7 +16802,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6">
       <c r="A395">
         <v>393</v>
       </c>
@@ -16763,7 +16819,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6">
       <c r="A396">
         <v>394</v>
       </c>
@@ -16780,7 +16836,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6">
       <c r="A397">
         <v>395</v>
       </c>
@@ -16797,7 +16853,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6">
       <c r="A398">
         <v>396</v>
       </c>
@@ -16814,7 +16870,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6">
       <c r="A399">
         <v>397</v>
       </c>
@@ -16831,7 +16887,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6">
       <c r="A400">
         <v>398</v>
       </c>
@@ -16848,7 +16904,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5">
       <c r="A401">
         <v>399</v>
       </c>
@@ -16865,7 +16921,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5">
       <c r="A402">
         <v>400</v>
       </c>
@@ -16882,7 +16938,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5">
       <c r="A403">
         <v>401</v>
       </c>
@@ -16899,7 +16955,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5">
       <c r="A404">
         <v>402</v>
       </c>
@@ -16916,7 +16972,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5">
       <c r="A405">
         <v>403</v>
       </c>
@@ -16933,7 +16989,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5">
       <c r="A406">
         <v>404</v>
       </c>
@@ -16950,7 +17006,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5">
       <c r="A407">
         <v>405</v>
       </c>
@@ -16967,7 +17023,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5">
       <c r="A408">
         <v>406</v>
       </c>
@@ -16984,7 +17040,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5">
       <c r="A409">
         <v>407</v>
       </c>
@@ -17001,7 +17057,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5">
       <c r="A410">
         <v>408</v>
       </c>
@@ -17018,7 +17074,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5">
       <c r="A411">
         <v>409</v>
       </c>
@@ -17035,7 +17091,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5">
       <c r="A412">
         <v>410</v>
       </c>
@@ -17052,7 +17108,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5">
       <c r="A413">
         <v>411</v>
       </c>
@@ -17069,7 +17125,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5">
       <c r="A414">
         <v>412</v>
       </c>
@@ -17086,7 +17142,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5">
       <c r="A415">
         <v>413</v>
       </c>
@@ -17103,7 +17159,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5">
       <c r="A416">
         <v>414</v>
       </c>
@@ -17120,7 +17176,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5">
       <c r="A417">
         <v>415</v>
       </c>
@@ -17137,7 +17193,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5">
       <c r="A418">
         <v>416</v>
       </c>
@@ -17154,7 +17210,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5">
       <c r="A419">
         <v>417</v>
       </c>
@@ -17171,7 +17227,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5">
       <c r="A420">
         <v>418</v>
       </c>
@@ -17188,7 +17244,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5">
       <c r="A421">
         <v>419</v>
       </c>
@@ -17205,7 +17261,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5">
       <c r="A422">
         <v>420</v>
       </c>
@@ -17222,7 +17278,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5">
       <c r="A423">
         <v>421</v>
       </c>
@@ -17239,7 +17295,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5">
       <c r="A424">
         <v>422</v>
       </c>
@@ -17256,7 +17312,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5">
       <c r="A425">
         <v>423</v>
       </c>
@@ -17273,7 +17329,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5">
       <c r="A426">
         <v>424</v>
       </c>
@@ -17290,7 +17346,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5">
       <c r="A427">
         <v>425</v>
       </c>
@@ -17307,7 +17363,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5">
       <c r="A428">
         <v>426</v>
       </c>
@@ -17324,7 +17380,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5">
       <c r="A429">
         <v>427</v>
       </c>
@@ -17341,7 +17397,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5">
       <c r="A430">
         <v>428</v>
       </c>
@@ -17358,7 +17414,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5">
       <c r="A431">
         <v>429</v>
       </c>
@@ -17375,7 +17431,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5">
       <c r="A432">
         <v>430</v>
       </c>
@@ -17392,7 +17448,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5">
       <c r="A433">
         <v>431</v>
       </c>
@@ -17409,7 +17465,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5">
       <c r="A434">
         <v>432</v>
       </c>
@@ -17426,7 +17482,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5">
       <c r="A435">
         <v>433</v>
       </c>
@@ -17443,7 +17499,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5">
       <c r="A436">
         <v>434</v>
       </c>
@@ -17460,7 +17516,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5">
       <c r="A437">
         <v>435</v>
       </c>
@@ -17477,7 +17533,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5">
       <c r="A438">
         <v>436</v>
       </c>
@@ -17494,7 +17550,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5">
       <c r="A439">
         <v>437</v>
       </c>
@@ -17511,7 +17567,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5">
       <c r="A440">
         <v>438</v>
       </c>
@@ -17528,7 +17584,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5">
       <c r="A441">
         <v>439</v>
       </c>
@@ -17545,7 +17601,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5">
       <c r="A442">
         <v>440</v>
       </c>
@@ -17562,7 +17618,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5">
       <c r="A443">
         <v>441</v>
       </c>
@@ -17579,7 +17635,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5">
       <c r="A444">
         <v>442</v>
       </c>
@@ -17596,7 +17652,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5">
       <c r="A445">
         <v>443</v>
       </c>
@@ -17613,7 +17669,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5">
       <c r="A446">
         <v>444</v>
       </c>
@@ -17630,7 +17686,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5">
       <c r="A447">
         <v>445</v>
       </c>
@@ -17647,7 +17703,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5">
       <c r="A448">
         <v>446</v>
       </c>
@@ -17664,7 +17720,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6">
       <c r="A449">
         <v>447</v>
       </c>
@@ -17681,7 +17737,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6">
       <c r="A450">
         <v>448</v>
       </c>
@@ -17701,7 +17757,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6">
       <c r="A451">
         <v>449</v>
       </c>
@@ -17718,7 +17774,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6">
       <c r="A452">
         <v>450</v>
       </c>
@@ -17735,7 +17791,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6">
       <c r="A453">
         <v>451</v>
       </c>
@@ -17752,7 +17808,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6">
       <c r="A454">
         <v>452</v>
       </c>
@@ -17769,7 +17825,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6">
       <c r="A455">
         <v>453</v>
       </c>
@@ -17786,7 +17842,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6">
       <c r="A456">
         <v>454</v>
       </c>
@@ -17803,7 +17859,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6">
       <c r="A457">
         <v>455</v>
       </c>
@@ -17820,7 +17876,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6">
       <c r="A458">
         <v>456</v>
       </c>
@@ -17837,7 +17893,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6">
       <c r="A459">
         <v>457</v>
       </c>
@@ -17854,7 +17910,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6">
       <c r="A460">
         <v>458</v>
       </c>
@@ -17871,7 +17927,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6">
       <c r="A461">
         <v>459</v>
       </c>
@@ -17888,7 +17944,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6">
       <c r="A462">
         <v>460</v>
       </c>
@@ -17905,7 +17961,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6">
       <c r="A463">
         <v>461</v>
       </c>
@@ -17922,7 +17978,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6">
       <c r="A464">
         <v>462</v>
       </c>
@@ -17939,7 +17995,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5">
       <c r="A465">
         <v>463</v>
       </c>
@@ -17956,7 +18012,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5">
       <c r="A466">
         <v>464</v>
       </c>
@@ -17973,7 +18029,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5">
       <c r="A467">
         <v>465</v>
       </c>
@@ -17990,7 +18046,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5">
       <c r="A468">
         <v>466</v>
       </c>
@@ -18007,7 +18063,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5">
       <c r="A469">
         <v>467</v>
       </c>
@@ -18024,7 +18080,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5">
       <c r="A470">
         <v>468</v>
       </c>
@@ -18041,7 +18097,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5">
       <c r="A471">
         <v>469</v>
       </c>
@@ -18058,7 +18114,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5">
       <c r="A472">
         <v>470</v>
       </c>
@@ -18075,7 +18131,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5">
       <c r="A473">
         <v>471</v>
       </c>
@@ -18092,7 +18148,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5">
       <c r="A474">
         <v>472</v>
       </c>
@@ -18109,7 +18165,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5">
       <c r="A475">
         <v>473</v>
       </c>
@@ -18126,7 +18182,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5">
       <c r="A476">
         <v>474</v>
       </c>
@@ -18143,7 +18199,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5">
       <c r="A477">
         <v>475</v>
       </c>
@@ -18160,7 +18216,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5">
       <c r="A478">
         <v>476</v>
       </c>
@@ -18177,7 +18233,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5">
       <c r="A479">
         <v>477</v>
       </c>
@@ -18194,7 +18250,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5">
       <c r="A480">
         <v>478</v>
       </c>
@@ -18211,7 +18267,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5">
       <c r="A481">
         <v>479</v>
       </c>
@@ -18228,7 +18284,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5">
       <c r="A482">
         <v>480</v>
       </c>
@@ -18245,7 +18301,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5">
       <c r="A483">
         <v>481</v>
       </c>
@@ -18262,7 +18318,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5">
       <c r="A484">
         <v>482</v>
       </c>
@@ -18279,7 +18335,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5">
       <c r="A485">
         <v>483</v>
       </c>
@@ -18296,7 +18352,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5">
       <c r="A486">
         <v>484</v>
       </c>
@@ -18313,7 +18369,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5">
       <c r="A487">
         <v>485</v>
       </c>
@@ -18330,7 +18386,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5">
       <c r="A488">
         <v>486</v>
       </c>
@@ -18347,7 +18403,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5">
       <c r="A489">
         <v>487</v>
       </c>
@@ -18364,7 +18420,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5">
       <c r="A490">
         <v>488</v>
       </c>
@@ -18381,7 +18437,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5">
       <c r="A491">
         <v>489</v>
       </c>
@@ -18398,7 +18454,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5">
       <c r="A492">
         <v>490</v>
       </c>
@@ -18415,7 +18471,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5">
       <c r="A493">
         <v>491</v>
       </c>
@@ -18432,7 +18488,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5">
       <c r="A494">
         <v>492</v>
       </c>
@@ -18449,7 +18505,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5">
       <c r="A495">
         <v>493</v>
       </c>
@@ -18466,7 +18522,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5">
       <c r="A496">
         <v>494</v>
       </c>
@@ -18483,7 +18539,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5">
       <c r="A497">
         <v>495</v>
       </c>
@@ -18500,7 +18556,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5">
       <c r="A498">
         <v>496</v>
       </c>
@@ -18517,7 +18573,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5">
       <c r="A499">
         <v>497</v>
       </c>
@@ -18534,7 +18590,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5">
       <c r="A500">
         <v>498</v>
       </c>
@@ -18551,7 +18607,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5">
       <c r="A501">
         <v>499</v>
       </c>
@@ -18568,7 +18624,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5">
       <c r="A502">
         <v>500</v>
       </c>
@@ -18585,7 +18641,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5">
       <c r="A503">
         <v>501</v>
       </c>
@@ -18602,7 +18658,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5">
       <c r="A504">
         <v>502</v>
       </c>
@@ -18619,7 +18675,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5">
       <c r="A505">
         <v>503</v>
       </c>
@@ -18636,7 +18692,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5">
       <c r="A506">
         <v>504</v>
       </c>
@@ -18653,7 +18709,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5">
       <c r="A507">
         <v>505</v>
       </c>
@@ -18670,7 +18726,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5">
       <c r="A508">
         <v>506</v>
       </c>
@@ -18687,7 +18743,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5">
       <c r="A509">
         <v>507</v>
       </c>
@@ -18704,7 +18760,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5">
       <c r="A510">
         <v>508</v>
       </c>
@@ -18721,7 +18777,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5">
       <c r="A511">
         <v>509</v>
       </c>
@@ -18738,7 +18794,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5">
       <c r="A512">
         <v>510</v>
       </c>
@@ -18755,7 +18811,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:6">
       <c r="A513">
         <v>511</v>
       </c>
@@ -18772,7 +18828,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:6">
       <c r="A514">
         <v>512</v>
       </c>
@@ -18792,7 +18848,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:6">
       <c r="A515">
         <v>513</v>
       </c>
@@ -18809,7 +18865,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:6">
       <c r="A516">
         <v>514</v>
       </c>
@@ -18826,7 +18882,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:6">
       <c r="A517">
         <v>515</v>
       </c>
@@ -18843,7 +18899,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:6">
       <c r="A518">
         <v>516</v>
       </c>
@@ -18860,7 +18916,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:6">
       <c r="A519">
         <v>517</v>
       </c>
@@ -18877,7 +18933,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:6">
       <c r="A520">
         <v>518</v>
       </c>
@@ -18894,7 +18950,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:6">
       <c r="A521">
         <v>519</v>
       </c>
@@ -18911,7 +18967,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:6">
       <c r="A522">
         <v>520</v>
       </c>
@@ -18928,7 +18984,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:6">
       <c r="A523">
         <v>521</v>
       </c>
@@ -18945,7 +19001,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:6">
       <c r="A524">
         <v>522</v>
       </c>
@@ -18962,7 +19018,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:6">
       <c r="A525">
         <v>523</v>
       </c>
@@ -18979,7 +19035,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:6">
       <c r="A526">
         <v>524</v>
       </c>
@@ -18996,7 +19052,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:6">
       <c r="A527">
         <v>525</v>
       </c>
@@ -19013,7 +19069,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:6">
       <c r="A528">
         <v>526</v>
       </c>
@@ -19030,7 +19086,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5">
       <c r="A529">
         <v>527</v>
       </c>
@@ -19047,7 +19103,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5">
       <c r="A530">
         <v>528</v>
       </c>
@@ -19064,7 +19120,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5">
       <c r="A531">
         <v>529</v>
       </c>
@@ -19081,7 +19137,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5">
       <c r="A532">
         <v>530</v>
       </c>
@@ -19098,7 +19154,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5">
       <c r="A533">
         <v>531</v>
       </c>
@@ -19115,7 +19171,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5">
       <c r="A534">
         <v>532</v>
       </c>
@@ -19132,7 +19188,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5">
       <c r="A535">
         <v>533</v>
       </c>
@@ -19149,7 +19205,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5">
       <c r="A536">
         <v>534</v>
       </c>
@@ -19166,7 +19222,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5">
       <c r="A537">
         <v>535</v>
       </c>
@@ -19183,7 +19239,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5">
       <c r="A538">
         <v>536</v>
       </c>
@@ -19200,7 +19256,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5">
       <c r="A539">
         <v>537</v>
       </c>
@@ -19217,7 +19273,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5">
       <c r="A540">
         <v>538</v>
       </c>
@@ -19234,7 +19290,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5">
       <c r="A541">
         <v>539</v>
       </c>
@@ -19251,7 +19307,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5">
       <c r="A542">
         <v>540</v>
       </c>
@@ -19268,7 +19324,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5">
       <c r="A543">
         <v>541</v>
       </c>
@@ -19285,7 +19341,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5">
       <c r="A544">
         <v>542</v>
       </c>
@@ -19302,7 +19358,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5">
       <c r="A545">
         <v>543</v>
       </c>
@@ -19319,7 +19375,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5">
       <c r="A546">
         <v>544</v>
       </c>
@@ -19336,7 +19392,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5">
       <c r="A547">
         <v>545</v>
       </c>
@@ -19353,7 +19409,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5">
       <c r="A548">
         <v>546</v>
       </c>
@@ -19370,7 +19426,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5">
       <c r="A549">
         <v>547</v>
       </c>
@@ -19387,7 +19443,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5">
       <c r="A550">
         <v>548</v>
       </c>
@@ -19404,7 +19460,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5">
       <c r="A551">
         <v>549</v>
       </c>
@@ -19421,7 +19477,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5">
       <c r="A552">
         <v>550</v>
       </c>
@@ -19438,7 +19494,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5">
       <c r="A553">
         <v>551</v>
       </c>
@@ -19455,7 +19511,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5">
       <c r="A554">
         <v>552</v>
       </c>
@@ -19472,7 +19528,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5">
       <c r="A555">
         <v>553</v>
       </c>
@@ -19489,7 +19545,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5">
       <c r="A556">
         <v>554</v>
       </c>
@@ -19506,7 +19562,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5">
       <c r="A557">
         <v>555</v>
       </c>
@@ -19523,7 +19579,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5">
       <c r="A558">
         <v>556</v>
       </c>
@@ -19540,7 +19596,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5">
       <c r="A559">
         <v>557</v>
       </c>
@@ -19557,7 +19613,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5">
       <c r="A560">
         <v>558</v>
       </c>
@@ -19574,7 +19630,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5">
       <c r="A561">
         <v>559</v>
       </c>
@@ -19591,7 +19647,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5">
       <c r="A562">
         <v>560</v>
       </c>
@@ -19608,7 +19664,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5">
       <c r="A563">
         <v>561</v>
       </c>
@@ -19625,7 +19681,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5">
       <c r="A564">
         <v>562</v>
       </c>
@@ -19642,7 +19698,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5">
       <c r="A565">
         <v>563</v>
       </c>
@@ -19659,7 +19715,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5">
       <c r="A566">
         <v>564</v>
       </c>
@@ -19676,7 +19732,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5">
       <c r="A567">
         <v>565</v>
       </c>
@@ -19693,7 +19749,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5">
       <c r="A568">
         <v>566</v>
       </c>
@@ -19710,7 +19766,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5">
       <c r="A569">
         <v>567</v>
       </c>
@@ -19727,7 +19783,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5">
       <c r="A570">
         <v>568</v>
       </c>
@@ -19744,7 +19800,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5">
       <c r="A571">
         <v>569</v>
       </c>
@@ -19761,7 +19817,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5">
       <c r="A572">
         <v>570</v>
       </c>
@@ -19778,7 +19834,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5">
       <c r="A573">
         <v>571</v>
       </c>
@@ -19795,7 +19851,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5">
       <c r="A574">
         <v>572</v>
       </c>
@@ -19812,7 +19868,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5">
       <c r="A575">
         <v>573</v>
       </c>
@@ -19829,7 +19885,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5">
       <c r="A576">
         <v>574</v>
       </c>
@@ -19846,7 +19902,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:6">
       <c r="A577">
         <v>575</v>
       </c>
@@ -19863,7 +19919,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:6">
       <c r="A578">
         <v>576</v>
       </c>
@@ -19883,7 +19939,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:6">
       <c r="A579">
         <v>577</v>
       </c>
@@ -19900,7 +19956,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:6">
       <c r="A580">
         <v>578</v>
       </c>
@@ -19917,7 +19973,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:6">
       <c r="A581">
         <v>579</v>
       </c>
@@ -19934,7 +19990,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:6">
       <c r="A582">
         <v>580</v>
       </c>
@@ -19951,7 +20007,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:6">
       <c r="A583">
         <v>581</v>
       </c>
@@ -19968,7 +20024,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:6">
       <c r="A584">
         <v>582</v>
       </c>
@@ -19985,7 +20041,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:6">
       <c r="A585">
         <v>583</v>
       </c>
@@ -20002,7 +20058,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:6">
       <c r="A586">
         <v>584</v>
       </c>
@@ -20019,7 +20075,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:6">
       <c r="A587">
         <v>585</v>
       </c>
@@ -20036,7 +20092,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:6">
       <c r="A588">
         <v>586</v>
       </c>
@@ -20053,7 +20109,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:6">
       <c r="A589">
         <v>587</v>
       </c>
@@ -20070,7 +20126,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:6">
       <c r="A590">
         <v>588</v>
       </c>
@@ -20087,7 +20143,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:6">
       <c r="A591">
         <v>589</v>
       </c>
@@ -20104,7 +20160,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:6">
       <c r="A592">
         <v>590</v>
       </c>
@@ -20121,7 +20177,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5">
       <c r="A593">
         <v>591</v>
       </c>
@@ -20138,7 +20194,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5">
       <c r="A594">
         <v>592</v>
       </c>
@@ -20155,7 +20211,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5">
       <c r="A595">
         <v>593</v>
       </c>
@@ -20172,7 +20228,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5">
       <c r="A596">
         <v>594</v>
       </c>
@@ -20189,7 +20245,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5">
       <c r="A597">
         <v>595</v>
       </c>
@@ -20206,7 +20262,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5">
       <c r="A598">
         <v>596</v>
       </c>
@@ -20223,7 +20279,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5">
       <c r="A599">
         <v>597</v>
       </c>
@@ -20240,7 +20296,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5">
       <c r="A600">
         <v>598</v>
       </c>
@@ -20257,7 +20313,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5">
       <c r="A601">
         <v>599</v>
       </c>
@@ -20274,7 +20330,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5">
       <c r="A602">
         <v>600</v>
       </c>
@@ -20291,7 +20347,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5">
       <c r="A603">
         <v>601</v>
       </c>
@@ -20308,7 +20364,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5">
       <c r="A604">
         <v>602</v>
       </c>
@@ -20325,7 +20381,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5">
       <c r="A605">
         <v>603</v>
       </c>
@@ -20342,7 +20398,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5">
       <c r="A606">
         <v>604</v>
       </c>
@@ -20359,7 +20415,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5">
       <c r="A607">
         <v>605</v>
       </c>
@@ -20376,7 +20432,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5">
       <c r="A608">
         <v>606</v>
       </c>
@@ -20393,7 +20449,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5">
       <c r="A609">
         <v>607</v>
       </c>
@@ -20410,7 +20466,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5">
       <c r="A610">
         <v>608</v>
       </c>
@@ -20427,7 +20483,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5">
       <c r="A611">
         <v>609</v>
       </c>
@@ -20444,7 +20500,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5">
       <c r="A612">
         <v>610</v>
       </c>
@@ -20461,7 +20517,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5">
       <c r="A613">
         <v>611</v>
       </c>
@@ -20478,7 +20534,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5">
       <c r="A614">
         <v>612</v>
       </c>
@@ -20495,7 +20551,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5">
       <c r="A615">
         <v>613</v>
       </c>
@@ -20512,7 +20568,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5">
       <c r="A616">
         <v>614</v>
       </c>
@@ -20529,7 +20585,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5">
       <c r="A617">
         <v>615</v>
       </c>
@@ -20546,7 +20602,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5">
       <c r="A618">
         <v>616</v>
       </c>
@@ -20563,7 +20619,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5">
       <c r="A619">
         <v>617</v>
       </c>
@@ -20580,7 +20636,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5">
       <c r="A620">
         <v>618</v>
       </c>
@@ -20597,7 +20653,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5">
       <c r="A621">
         <v>619</v>
       </c>
@@ -20614,7 +20670,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5">
       <c r="A622">
         <v>620</v>
       </c>
@@ -20631,7 +20687,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5">
       <c r="A623">
         <v>621</v>
       </c>
@@ -20648,7 +20704,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5">
       <c r="A624">
         <v>622</v>
       </c>
@@ -20665,7 +20721,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5">
       <c r="A625">
         <v>623</v>
       </c>
@@ -20682,7 +20738,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5">
       <c r="A626">
         <v>624</v>
       </c>
@@ -20699,7 +20755,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5">
       <c r="A627">
         <v>625</v>
       </c>
@@ -20716,7 +20772,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5">
       <c r="A628">
         <v>626</v>
       </c>
@@ -20733,7 +20789,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5">
       <c r="A629">
         <v>627</v>
       </c>
@@ -20750,7 +20806,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5">
       <c r="A630">
         <v>628</v>
       </c>
@@ -20767,7 +20823,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5">
       <c r="A631">
         <v>629</v>
       </c>
@@ -20784,7 +20840,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5">
       <c r="A632">
         <v>630</v>
       </c>
@@ -20801,7 +20857,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5">
       <c r="A633">
         <v>631</v>
       </c>
@@ -20818,7 +20874,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5">
       <c r="A634">
         <v>632</v>
       </c>
@@ -20835,7 +20891,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5">
       <c r="A635">
         <v>633</v>
       </c>
@@ -20852,7 +20908,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5">
       <c r="A636">
         <v>634</v>
       </c>
@@ -20869,7 +20925,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5">
       <c r="A637">
         <v>635</v>
       </c>
@@ -20886,7 +20942,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5">
       <c r="A638">
         <v>636</v>
       </c>
@@ -20903,7 +20959,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5">
       <c r="A639">
         <v>637</v>
       </c>
@@ -20920,7 +20976,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5">
       <c r="A640">
         <v>638</v>
       </c>
@@ -20937,7 +20993,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:6">
       <c r="A641">
         <v>639</v>
       </c>
@@ -20954,7 +21010,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:6">
       <c r="A642">
         <v>640</v>
       </c>
@@ -20974,7 +21030,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:6">
       <c r="A643">
         <v>641</v>
       </c>
@@ -20991,7 +21047,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:6">
       <c r="A644">
         <v>642</v>
       </c>
@@ -21008,7 +21064,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:6">
       <c r="A645">
         <v>643</v>
       </c>
@@ -21025,7 +21081,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:6">
       <c r="A646">
         <v>644</v>
       </c>
@@ -21042,7 +21098,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:6">
       <c r="A647">
         <v>645</v>
       </c>
@@ -21059,7 +21115,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:6">
       <c r="A648">
         <v>646</v>
       </c>
@@ -21076,7 +21132,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:6">
       <c r="A649">
         <v>647</v>
       </c>
@@ -21093,7 +21149,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:6">
       <c r="A650">
         <v>648</v>
       </c>
@@ -21110,7 +21166,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:6">
       <c r="A651">
         <v>649</v>
       </c>
@@ -21127,7 +21183,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:6">
       <c r="A652">
         <v>650</v>
       </c>
@@ -21144,7 +21200,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:6">
       <c r="A653">
         <v>651</v>
       </c>
@@ -21161,7 +21217,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:6">
       <c r="A654">
         <v>652</v>
       </c>
@@ -21178,7 +21234,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:6">
       <c r="A655">
         <v>653</v>
       </c>
@@ -21195,7 +21251,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:6">
       <c r="A656">
         <v>654</v>
       </c>
@@ -21212,7 +21268,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5">
       <c r="A657">
         <v>655</v>
       </c>
@@ -21229,7 +21285,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5">
       <c r="A658">
         <v>656</v>
       </c>
@@ -21246,7 +21302,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5">
       <c r="A659">
         <v>657</v>
       </c>
@@ -21263,7 +21319,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5">
       <c r="A660">
         <v>658</v>
       </c>
@@ -21280,7 +21336,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5">
       <c r="A661">
         <v>659</v>
       </c>
@@ -21297,7 +21353,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5">
       <c r="A662">
         <v>660</v>
       </c>
@@ -21314,7 +21370,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5">
       <c r="A663">
         <v>661</v>
       </c>
@@ -21331,7 +21387,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5">
       <c r="A664">
         <v>662</v>
       </c>
@@ -21348,7 +21404,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5">
       <c r="A665">
         <v>663</v>
       </c>
@@ -21365,7 +21421,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5">
       <c r="A666">
         <v>664</v>
       </c>
@@ -21382,7 +21438,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5">
       <c r="A667">
         <v>665</v>
       </c>
@@ -21399,7 +21455,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5">
       <c r="A668">
         <v>666</v>
       </c>
@@ -21416,7 +21472,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5">
       <c r="A669">
         <v>667</v>
       </c>
@@ -21433,7 +21489,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5">
       <c r="A670">
         <v>668</v>
       </c>
@@ -21450,7 +21506,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5">
       <c r="A671">
         <v>669</v>
       </c>
@@ -21467,7 +21523,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5">
       <c r="A672">
         <v>670</v>
       </c>
@@ -21484,7 +21540,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5">
       <c r="A673">
         <v>671</v>
       </c>
@@ -21501,7 +21557,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5">
       <c r="A674">
         <v>672</v>
       </c>
@@ -21518,7 +21574,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5">
       <c r="A675">
         <v>673</v>
       </c>
@@ -21535,7 +21591,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5">
       <c r="A676">
         <v>674</v>
       </c>
@@ -21552,7 +21608,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5">
       <c r="A677">
         <v>675</v>
       </c>
@@ -21569,7 +21625,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5">
       <c r="A678">
         <v>676</v>
       </c>
@@ -21586,7 +21642,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5">
       <c r="A679">
         <v>677</v>
       </c>
@@ -21603,7 +21659,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5">
       <c r="A680">
         <v>678</v>
       </c>
@@ -21620,7 +21676,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5">
       <c r="A681">
         <v>679</v>
       </c>
@@ -21637,7 +21693,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5">
       <c r="A682">
         <v>680</v>
       </c>
@@ -21654,7 +21710,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5">
       <c r="A683">
         <v>681</v>
       </c>
@@ -21671,7 +21727,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5">
       <c r="A684">
         <v>682</v>
       </c>
@@ -21688,7 +21744,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5">
       <c r="A685">
         <v>683</v>
       </c>
@@ -21705,7 +21761,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5">
       <c r="A686">
         <v>684</v>
       </c>
@@ -21722,7 +21778,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5">
       <c r="A687">
         <v>685</v>
       </c>
@@ -21739,7 +21795,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5">
       <c r="A688">
         <v>686</v>
       </c>
@@ -21756,7 +21812,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5">
       <c r="A689">
         <v>687</v>
       </c>
@@ -21773,7 +21829,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5">
       <c r="A690">
         <v>688</v>
       </c>
@@ -21790,7 +21846,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5">
       <c r="A691">
         <v>689</v>
       </c>
@@ -21807,7 +21863,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5">
       <c r="A692">
         <v>690</v>
       </c>
@@ -21824,7 +21880,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5">
       <c r="A693">
         <v>691</v>
       </c>
@@ -21841,7 +21897,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5">
       <c r="A694">
         <v>692</v>
       </c>
@@ -21858,7 +21914,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5">
       <c r="A695">
         <v>693</v>
       </c>
@@ -21875,7 +21931,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5">
       <c r="A696">
         <v>694</v>
       </c>
@@ -21892,7 +21948,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5">
       <c r="A697">
         <v>695</v>
       </c>
@@ -21909,7 +21965,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5">
       <c r="A698">
         <v>696</v>
       </c>
@@ -21926,7 +21982,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5">
       <c r="A699">
         <v>697</v>
       </c>
@@ -21943,7 +21999,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5">
       <c r="A700">
         <v>698</v>
       </c>
@@ -21960,7 +22016,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5">
       <c r="A701">
         <v>699</v>
       </c>
@@ -21977,7 +22033,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5">
       <c r="A702">
         <v>700</v>
       </c>
@@ -21994,7 +22050,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5">
       <c r="A703">
         <v>701</v>
       </c>
@@ -22011,7 +22067,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5">
       <c r="A704">
         <v>702</v>
       </c>
@@ -22028,7 +22084,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:6">
       <c r="A705">
         <v>703</v>
       </c>
@@ -22045,7 +22101,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:6">
       <c r="A706">
         <v>704</v>
       </c>
@@ -22065,7 +22121,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:6">
       <c r="A707">
         <v>705</v>
       </c>
@@ -22082,7 +22138,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:6">
       <c r="A708">
         <v>706</v>
       </c>
@@ -22099,7 +22155,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:6">
       <c r="A709">
         <v>707</v>
       </c>
@@ -22116,7 +22172,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:6">
       <c r="A710">
         <v>708</v>
       </c>
@@ -22133,7 +22189,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:6">
       <c r="A711">
         <v>709</v>
       </c>
@@ -22150,7 +22206,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:6">
       <c r="A712">
         <v>710</v>
       </c>
@@ -22167,7 +22223,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:6">
       <c r="A713">
         <v>711</v>
       </c>
@@ -22184,7 +22240,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:6">
       <c r="A714">
         <v>712</v>
       </c>
@@ -22201,7 +22257,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:6">
       <c r="A715">
         <v>713</v>
       </c>
@@ -22218,7 +22274,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:6">
       <c r="A716">
         <v>714</v>
       </c>
@@ -22235,7 +22291,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:6">
       <c r="A717">
         <v>715</v>
       </c>
@@ -22252,7 +22308,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:6">
       <c r="A718">
         <v>716</v>
       </c>
@@ -22269,7 +22325,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:6">
       <c r="A719">
         <v>717</v>
       </c>
@@ -22286,7 +22342,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:6">
       <c r="A720">
         <v>718</v>
       </c>
@@ -22303,7 +22359,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5">
       <c r="A721">
         <v>719</v>
       </c>
@@ -22320,7 +22376,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5">
       <c r="A722">
         <v>720</v>
       </c>
@@ -22337,7 +22393,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5">
       <c r="A723">
         <v>721</v>
       </c>
@@ -22354,7 +22410,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5">
       <c r="A724">
         <v>722</v>
       </c>
@@ -22371,7 +22427,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5">
       <c r="A725">
         <v>723</v>
       </c>
@@ -22388,7 +22444,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5">
       <c r="A726">
         <v>724</v>
       </c>
@@ -22405,7 +22461,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5">
       <c r="A727">
         <v>725</v>
       </c>
@@ -22422,7 +22478,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5">
       <c r="A728">
         <v>726</v>
       </c>
@@ -22439,7 +22495,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5">
       <c r="A729">
         <v>727</v>
       </c>
@@ -22456,7 +22512,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5">
       <c r="A730">
         <v>728</v>
       </c>
@@ -22473,7 +22529,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5">
       <c r="A731">
         <v>729</v>
       </c>
@@ -22490,7 +22546,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5">
       <c r="A732">
         <v>730</v>
       </c>
@@ -22507,7 +22563,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5">
       <c r="A733">
         <v>731</v>
       </c>
@@ -22524,7 +22580,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5">
       <c r="A734">
         <v>732</v>
       </c>
@@ -22541,7 +22597,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5">
       <c r="A735">
         <v>733</v>
       </c>
@@ -22558,7 +22614,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5">
       <c r="A736">
         <v>734</v>
       </c>
@@ -22575,7 +22631,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5">
       <c r="A737">
         <v>735</v>
       </c>
@@ -22592,7 +22648,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5">
       <c r="A738">
         <v>736</v>
       </c>
@@ -22609,7 +22665,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5">
       <c r="A739">
         <v>737</v>
       </c>
@@ -22626,7 +22682,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5">
       <c r="A740">
         <v>738</v>
       </c>
@@ -22643,7 +22699,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5">
       <c r="A741">
         <v>739</v>
       </c>
@@ -22660,7 +22716,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5">
       <c r="A742">
         <v>740</v>
       </c>
@@ -22677,7 +22733,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5">
       <c r="A743">
         <v>741</v>
       </c>
@@ -22694,7 +22750,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5">
       <c r="A744">
         <v>742</v>
       </c>
@@ -22711,7 +22767,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5">
       <c r="A745">
         <v>743</v>
       </c>
@@ -22728,7 +22784,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5">
       <c r="A746">
         <v>744</v>
       </c>
@@ -22745,7 +22801,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5">
       <c r="A747">
         <v>745</v>
       </c>
@@ -22762,7 +22818,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5">
       <c r="A748">
         <v>746</v>
       </c>
@@ -22779,7 +22835,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5">
       <c r="A749">
         <v>747</v>
       </c>
@@ -22796,7 +22852,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5">
       <c r="A750">
         <v>748</v>
       </c>
@@ -22813,7 +22869,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5">
       <c r="A751">
         <v>749</v>
       </c>
@@ -22830,7 +22886,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5">
       <c r="A752">
         <v>750</v>
       </c>
@@ -22847,7 +22903,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="753" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:5">
       <c r="A753">
         <v>751</v>
       </c>
@@ -22864,7 +22920,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="754" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:5">
       <c r="A754">
         <v>752</v>
       </c>
@@ -22881,7 +22937,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="755" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:5">
       <c r="A755">
         <v>753</v>
       </c>
@@ -22898,7 +22954,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="756" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:5">
       <c r="A756">
         <v>754</v>
       </c>
@@ -22915,7 +22971,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="757" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:5">
       <c r="A757">
         <v>755</v>
       </c>
@@ -22932,7 +22988,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="758" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:5">
       <c r="A758">
         <v>756</v>
       </c>
@@ -22949,7 +23005,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="759" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:5">
       <c r="A759">
         <v>757</v>
       </c>
@@ -22966,7 +23022,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="760" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:5">
       <c r="A760">
         <v>758</v>
       </c>
@@ -22983,7 +23039,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="761" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:5">
       <c r="A761">
         <v>759</v>
       </c>
@@ -23000,7 +23056,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="762" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:5">
       <c r="A762">
         <v>760</v>
       </c>
@@ -23017,7 +23073,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="763" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:5">
       <c r="A763">
         <v>761</v>
       </c>
@@ -23034,7 +23090,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="764" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:5">
       <c r="A764">
         <v>762</v>
       </c>
@@ -23051,7 +23107,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="765" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:5">
       <c r="A765">
         <v>763</v>
       </c>
@@ -23068,7 +23124,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="766" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:5">
       <c r="A766">
         <v>764</v>
       </c>
@@ -23085,7 +23141,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="767" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:5">
       <c r="A767">
         <v>765</v>
       </c>
@@ -23102,7 +23158,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="768" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:5">
       <c r="A768">
         <v>766</v>
       </c>
@@ -23119,7 +23175,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:6">
       <c r="A769">
         <v>767</v>
       </c>
@@ -23136,7 +23192,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:6">
       <c r="A770">
         <v>768</v>
       </c>
@@ -23156,7 +23212,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:6">
       <c r="A771">
         <v>769</v>
       </c>
@@ -23173,7 +23229,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="772" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:6">
       <c r="A772">
         <v>770</v>
       </c>
@@ -23190,7 +23246,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:6">
       <c r="A773">
         <v>771</v>
       </c>
@@ -23207,7 +23263,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:6">
       <c r="A774">
         <v>772</v>
       </c>
@@ -23224,7 +23280,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="775" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:6">
       <c r="A775">
         <v>773</v>
       </c>
@@ -23241,7 +23297,7 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:6">
       <c r="A776">
         <v>774</v>
       </c>
@@ -23258,7 +23314,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:6">
       <c r="A777">
         <v>775</v>
       </c>
@@ -23275,7 +23331,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="778" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:6">
       <c r="A778">
         <v>776</v>
       </c>
@@ -23292,7 +23348,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:6">
       <c r="A779">
         <v>777</v>
       </c>
@@ -23309,7 +23365,7 @@
         <v>2336</v>
       </c>
     </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:6">
       <c r="A780">
         <v>778</v>
       </c>
@@ -23326,7 +23382,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="781" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:6">
       <c r="A781">
         <v>779</v>
       </c>
@@ -23343,7 +23399,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="782" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:6">
       <c r="A782">
         <v>780</v>
       </c>
@@ -23360,7 +23416,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="783" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:6">
       <c r="A783">
         <v>781</v>
       </c>
@@ -23377,7 +23433,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:6">
       <c r="A784">
         <v>782</v>
       </c>
@@ -23394,7 +23450,7 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="785" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:5">
       <c r="A785">
         <v>783</v>
       </c>
@@ -23411,7 +23467,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="786" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:5">
       <c r="A786">
         <v>784</v>
       </c>
@@ -23428,7 +23484,7 @@
         <v>2357</v>
       </c>
     </row>
-    <row r="787" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:5">
       <c r="A787">
         <v>785</v>
       </c>
@@ -23445,7 +23501,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="788" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:5">
       <c r="A788">
         <v>786</v>
       </c>
@@ -23462,7 +23518,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="789" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:5">
       <c r="A789">
         <v>787</v>
       </c>
@@ -23479,7 +23535,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="790" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:5">
       <c r="A790">
         <v>788</v>
       </c>
@@ -23496,7 +23552,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="791" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:5">
       <c r="A791">
         <v>789</v>
       </c>
@@ -23513,7 +23569,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="792" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:5">
       <c r="A792">
         <v>790</v>
       </c>
@@ -23530,7 +23586,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="793" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:5">
       <c r="A793">
         <v>791</v>
       </c>
@@ -23547,7 +23603,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="794" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:5">
       <c r="A794">
         <v>792</v>
       </c>
@@ -23564,7 +23620,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="795" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:5">
       <c r="A795">
         <v>793</v>
       </c>
@@ -23581,7 +23637,7 @@
         <v>2384</v>
       </c>
     </row>
-    <row r="796" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:5">
       <c r="A796">
         <v>794</v>
       </c>
@@ -23598,7 +23654,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="797" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:5">
       <c r="A797">
         <v>795</v>
       </c>
@@ -23615,7 +23671,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="798" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:5">
       <c r="A798">
         <v>796</v>
       </c>
@@ -23632,7 +23688,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="799" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:5">
       <c r="A799">
         <v>797</v>
       </c>
@@ -23649,7 +23705,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="800" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:5">
       <c r="A800">
         <v>798</v>
       </c>
@@ -23666,7 +23722,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="801" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:5">
       <c r="A801">
         <v>799</v>
       </c>
@@ -23683,7 +23739,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="802" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:5">
       <c r="A802">
         <v>800</v>
       </c>
@@ -23700,7 +23756,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="803" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:5">
       <c r="A803">
         <v>801</v>
       </c>
@@ -23717,7 +23773,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="804" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:5">
       <c r="A804">
         <v>802</v>
       </c>
@@ -23734,7 +23790,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="805" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:5">
       <c r="A805">
         <v>803</v>
       </c>
@@ -23751,7 +23807,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="806" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:5">
       <c r="A806">
         <v>804</v>
       </c>
@@ -23768,7 +23824,7 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="807" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:5">
       <c r="A807">
         <v>805</v>
       </c>
@@ -23785,7 +23841,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="808" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:5">
       <c r="A808">
         <v>806</v>
       </c>
@@ -23802,7 +23858,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="809" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:5">
       <c r="A809">
         <v>807</v>
       </c>
@@ -23819,7 +23875,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="810" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:5">
       <c r="A810">
         <v>808</v>
       </c>
@@ -23836,7 +23892,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="811" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:5">
       <c r="A811">
         <v>809</v>
       </c>
@@ -23853,7 +23909,7 @@
         <v>2432</v>
       </c>
     </row>
-    <row r="812" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:5">
       <c r="A812">
         <v>810</v>
       </c>
@@ -23870,7 +23926,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="813" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:5">
       <c r="A813">
         <v>811</v>
       </c>
@@ -23887,7 +23943,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="814" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:5">
       <c r="A814">
         <v>812</v>
       </c>
@@ -23904,7 +23960,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="815" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:5">
       <c r="A815">
         <v>813</v>
       </c>
@@ -23921,7 +23977,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="816" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:5">
       <c r="A816">
         <v>814</v>
       </c>
@@ -23938,7 +23994,7 @@
         <v>2447</v>
       </c>
     </row>
-    <row r="817" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:5">
       <c r="A817">
         <v>815</v>
       </c>
@@ -23955,7 +24011,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="818" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:5">
       <c r="A818">
         <v>816</v>
       </c>
@@ -23972,7 +24028,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="819" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:5">
       <c r="A819">
         <v>817</v>
       </c>
@@ -23989,7 +24045,7 @@
         <v>2456</v>
       </c>
     </row>
-    <row r="820" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:5">
       <c r="A820">
         <v>818</v>
       </c>
@@ -24006,7 +24062,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="821" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:5">
       <c r="A821">
         <v>819</v>
       </c>
@@ -24023,7 +24079,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="822" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:5">
       <c r="A822">
         <v>820</v>
       </c>
@@ -24040,7 +24096,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="823" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:5">
       <c r="A823">
         <v>821</v>
       </c>
@@ -24057,7 +24113,7 @@
         <v>2468</v>
       </c>
     </row>
-    <row r="824" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:5">
       <c r="A824">
         <v>822</v>
       </c>
@@ -24074,7 +24130,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="825" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:5">
       <c r="A825">
         <v>823</v>
       </c>
@@ -24091,7 +24147,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="826" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:5">
       <c r="A826">
         <v>824</v>
       </c>
@@ -24108,7 +24164,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="827" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:5">
       <c r="A827">
         <v>825</v>
       </c>
@@ -24125,7 +24181,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="828" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:5">
       <c r="A828">
         <v>826</v>
       </c>
@@ -24142,7 +24198,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="829" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:5">
       <c r="A829">
         <v>827</v>
       </c>
@@ -24159,7 +24215,7 @@
         <v>2486</v>
       </c>
     </row>
-    <row r="830" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:5">
       <c r="A830">
         <v>828</v>
       </c>
@@ -24176,7 +24232,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="831" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:5">
       <c r="A831">
         <v>829</v>
       </c>
@@ -24193,7 +24249,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="832" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:5">
       <c r="A832">
         <v>830</v>
       </c>
@@ -24210,7 +24266,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:6">
       <c r="A833">
         <v>831</v>
       </c>
@@ -24227,7 +24283,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:6">
       <c r="A834">
         <v>832</v>
       </c>
@@ -24247,7 +24303,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:6">
       <c r="A835">
         <v>833</v>
       </c>
@@ -24264,7 +24320,7 @@
         <v>2504</v>
       </c>
     </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:6">
       <c r="A836">
         <v>834</v>
       </c>
@@ -24281,7 +24337,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:6">
       <c r="A837">
         <v>835</v>
       </c>
@@ -24298,7 +24354,7 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:6">
       <c r="A838">
         <v>836</v>
       </c>
@@ -24315,7 +24371,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:6">
       <c r="A839">
         <v>837</v>
       </c>
@@ -24332,7 +24388,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:6">
       <c r="A840">
         <v>838</v>
       </c>
@@ -24349,7 +24405,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:6">
       <c r="A841">
         <v>839</v>
       </c>
@@ -24366,7 +24422,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:6">
       <c r="A842">
         <v>840</v>
       </c>
@@ -24383,7 +24439,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:6">
       <c r="A843">
         <v>841</v>
       </c>
@@ -24400,7 +24456,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:6">
       <c r="A844">
         <v>842</v>
       </c>
@@ -24417,7 +24473,7 @@
         <v>2531</v>
       </c>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:6">
       <c r="A845">
         <v>843</v>
       </c>
@@ -24434,7 +24490,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:6">
       <c r="A846">
         <v>844</v>
       </c>
@@ -24451,7 +24507,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:6">
       <c r="A847">
         <v>845</v>
       </c>
@@ -24468,7 +24524,7 @@
         <v>2540</v>
       </c>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:6">
       <c r="A848">
         <v>846</v>
       </c>
@@ -24485,7 +24541,7 @@
         <v>2543</v>
       </c>
     </row>
-    <row r="849" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:5">
       <c r="A849">
         <v>847</v>
       </c>
@@ -24502,7 +24558,7 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="850" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:5">
       <c r="A850">
         <v>848</v>
       </c>
@@ -24519,7 +24575,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="851" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:5">
       <c r="A851">
         <v>849</v>
       </c>
@@ -24536,7 +24592,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="852" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:5">
       <c r="A852">
         <v>850</v>
       </c>
@@ -24553,7 +24609,7 @@
         <v>2555</v>
       </c>
     </row>
-    <row r="853" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:5">
       <c r="A853">
         <v>851</v>
       </c>
@@ -24570,7 +24626,7 @@
         <v>2558</v>
       </c>
     </row>
-    <row r="854" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:5">
       <c r="A854">
         <v>852</v>
       </c>
@@ -24587,7 +24643,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="855" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:5">
       <c r="A855">
         <v>853</v>
       </c>
@@ -24604,7 +24660,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="856" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:5">
       <c r="A856">
         <v>854</v>
       </c>
@@ -24621,7 +24677,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="857" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:5">
       <c r="A857">
         <v>855</v>
       </c>
@@ -24638,7 +24694,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="858" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:5">
       <c r="A858">
         <v>856</v>
       </c>
@@ -24655,7 +24711,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="859" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:5">
       <c r="A859">
         <v>857</v>
       </c>
@@ -24672,7 +24728,7 @@
         <v>2576</v>
       </c>
     </row>
-    <row r="860" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:5">
       <c r="A860">
         <v>858</v>
       </c>
@@ -24689,7 +24745,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="861" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:5">
       <c r="A861">
         <v>859</v>
       </c>
@@ -24706,7 +24762,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="862" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:5">
       <c r="A862">
         <v>860</v>
       </c>
@@ -24723,7 +24779,7 @@
         <v>2585</v>
       </c>
     </row>
-    <row r="863" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:5">
       <c r="A863">
         <v>861</v>
       </c>
@@ -24740,7 +24796,7 @@
         <v>2588</v>
       </c>
     </row>
-    <row r="864" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:5">
       <c r="A864">
         <v>862</v>
       </c>
@@ -24757,7 +24813,7 @@
         <v>2591</v>
       </c>
     </row>
-    <row r="865" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:5">
       <c r="A865">
         <v>863</v>
       </c>
@@ -24774,7 +24830,7 @@
         <v>2594</v>
       </c>
     </row>
-    <row r="866" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:5">
       <c r="A866">
         <v>864</v>
       </c>
@@ -24791,7 +24847,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="867" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:5">
       <c r="A867">
         <v>865</v>
       </c>
@@ -24808,7 +24864,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="868" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:5">
       <c r="A868">
         <v>866</v>
       </c>
@@ -24825,7 +24881,7 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="869" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:5">
       <c r="A869">
         <v>867</v>
       </c>
@@ -24842,7 +24898,7 @@
         <v>2606</v>
       </c>
     </row>
-    <row r="870" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:5">
       <c r="A870">
         <v>868</v>
       </c>
@@ -24859,7 +24915,7 @@
         <v>2609</v>
       </c>
     </row>
-    <row r="871" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:5">
       <c r="A871">
         <v>869</v>
       </c>
@@ -24876,7 +24932,7 @@
         <v>2612</v>
       </c>
     </row>
-    <row r="872" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:5">
       <c r="A872">
         <v>870</v>
       </c>
@@ -24893,7 +24949,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="873" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:5">
       <c r="A873">
         <v>871</v>
       </c>
@@ -24910,7 +24966,7 @@
         <v>2618</v>
       </c>
     </row>
-    <row r="874" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:5">
       <c r="A874">
         <v>872</v>
       </c>
@@ -24927,7 +24983,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="875" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:5">
       <c r="A875">
         <v>873</v>
       </c>
@@ -24944,7 +25000,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="876" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:5">
       <c r="A876">
         <v>874</v>
       </c>
@@ -24961,7 +25017,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="877" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:5">
       <c r="A877">
         <v>875</v>
       </c>
@@ -24978,7 +25034,7 @@
         <v>2630</v>
       </c>
     </row>
-    <row r="878" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:5">
       <c r="A878">
         <v>876</v>
       </c>
@@ -24995,7 +25051,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="879" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:5">
       <c r="A879">
         <v>877</v>
       </c>
@@ -25012,7 +25068,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="880" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:5">
       <c r="A880">
         <v>878</v>
       </c>
@@ -25029,7 +25085,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="881" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:5">
       <c r="A881">
         <v>879</v>
       </c>
@@ -25046,7 +25102,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="882" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:5">
       <c r="A882">
         <v>880</v>
       </c>
@@ -25063,7 +25119,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="883" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:5">
       <c r="A883">
         <v>881</v>
       </c>
@@ -25080,7 +25136,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="884" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:5">
       <c r="A884">
         <v>882</v>
       </c>
@@ -25097,7 +25153,7 @@
         <v>2651</v>
       </c>
     </row>
-    <row r="885" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:5">
       <c r="A885">
         <v>883</v>
       </c>
@@ -25114,7 +25170,7 @@
         <v>2654</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:5">
       <c r="A886">
         <v>884</v>
       </c>
@@ -25131,7 +25187,7 @@
         <v>2657</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:5">
       <c r="A887">
         <v>885</v>
       </c>
@@ -25148,7 +25204,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:5">
       <c r="A888">
         <v>886</v>
       </c>
@@ -25165,7 +25221,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:5">
       <c r="A889">
         <v>887</v>
       </c>
@@ -25182,7 +25238,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:5">
       <c r="A890">
         <v>888</v>
       </c>
@@ -25199,7 +25255,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:5">
       <c r="A891">
         <v>889</v>
       </c>
@@ -25216,7 +25272,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:5">
       <c r="A892">
         <v>890</v>
       </c>
@@ -25233,7 +25289,7 @@
         <v>2675</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:5">
       <c r="A893">
         <v>891</v>
       </c>
@@ -25250,7 +25306,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:5">
       <c r="A894">
         <v>892</v>
       </c>
@@ -25267,7 +25323,7 @@
         <v>2681</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:5">
       <c r="A895">
         <v>893</v>
       </c>
@@ -25284,7 +25340,7 @@
         <v>2684</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:5">
       <c r="A896">
         <v>894</v>
       </c>
@@ -25301,7 +25357,7 @@
         <v>2687</v>
       </c>
     </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:6">
       <c r="A897">
         <v>895</v>
       </c>
@@ -25318,7 +25374,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:6">
       <c r="A898">
         <v>896</v>
       </c>
@@ -25338,7 +25394,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:6">
       <c r="A899">
         <v>897</v>
       </c>
@@ -25355,7 +25411,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:6">
       <c r="A900">
         <v>898</v>
       </c>
@@ -25372,7 +25428,7 @@
         <v>2699</v>
       </c>
     </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:6">
       <c r="A901">
         <v>899</v>
       </c>
@@ -25389,7 +25445,7 @@
         <v>2702</v>
       </c>
     </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:6">
       <c r="A902">
         <v>900</v>
       </c>
@@ -25406,7 +25462,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:6">
       <c r="A903">
         <v>901</v>
       </c>
@@ -25423,7 +25479,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:6">
       <c r="A904">
         <v>902</v>
       </c>
@@ -25440,7 +25496,7 @@
         <v>2711</v>
       </c>
     </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:6">
       <c r="A905">
         <v>903</v>
       </c>
@@ -25457,7 +25513,7 @@
         <v>2714</v>
       </c>
     </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:6">
       <c r="A906">
         <v>904</v>
       </c>
@@ -25474,7 +25530,7 @@
         <v>2717</v>
       </c>
     </row>
-    <row r="907" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:6">
       <c r="A907">
         <v>905</v>
       </c>
@@ -25491,7 +25547,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:6">
       <c r="A908">
         <v>906</v>
       </c>
@@ -25508,7 +25564,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:6">
       <c r="A909">
         <v>907</v>
       </c>
@@ -25525,7 +25581,7 @@
         <v>2726</v>
       </c>
     </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:6">
       <c r="A910">
         <v>908</v>
       </c>
@@ -25542,7 +25598,7 @@
         <v>2729</v>
       </c>
     </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:6">
       <c r="A911">
         <v>909</v>
       </c>
@@ -25559,7 +25615,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:6">
       <c r="A912">
         <v>910</v>
       </c>
@@ -25576,7 +25632,7 @@
         <v>2735</v>
       </c>
     </row>
-    <row r="913" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:5">
       <c r="A913">
         <v>911</v>
       </c>
@@ -25593,7 +25649,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="914" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:5">
       <c r="A914">
         <v>912</v>
       </c>
@@ -25610,7 +25666,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="915" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:5">
       <c r="A915">
         <v>913</v>
       </c>
@@ -25627,7 +25683,7 @@
         <v>2744</v>
       </c>
     </row>
-    <row r="916" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:5">
       <c r="A916">
         <v>914</v>
       </c>
@@ -25644,7 +25700,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="917" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:5">
       <c r="A917">
         <v>915</v>
       </c>
@@ -25661,7 +25717,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="918" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:5">
       <c r="A918">
         <v>916</v>
       </c>
@@ -25678,7 +25734,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="919" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:5">
       <c r="A919">
         <v>917</v>
       </c>
@@ -25695,7 +25751,7 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="920" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:5">
       <c r="A920">
         <v>918</v>
       </c>
@@ -25712,7 +25768,7 @@
         <v>2759</v>
       </c>
     </row>
-    <row r="921" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:5">
       <c r="A921">
         <v>919</v>
       </c>
@@ -25729,7 +25785,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="922" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:5">
       <c r="A922">
         <v>920</v>
       </c>
@@ -25746,7 +25802,7 @@
         <v>2765</v>
       </c>
     </row>
-    <row r="923" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:5">
       <c r="A923">
         <v>921</v>
       </c>
@@ -25763,7 +25819,7 @@
         <v>2768</v>
       </c>
     </row>
-    <row r="924" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:5">
       <c r="A924">
         <v>922</v>
       </c>
@@ -25780,7 +25836,7 @@
         <v>2771</v>
       </c>
     </row>
-    <row r="925" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:5">
       <c r="A925">
         <v>923</v>
       </c>
@@ -25797,7 +25853,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="926" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:5">
       <c r="A926">
         <v>924</v>
       </c>
@@ -25814,7 +25870,7 @@
         <v>2777</v>
       </c>
     </row>
-    <row r="927" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:5">
       <c r="A927">
         <v>925</v>
       </c>
@@ -25831,7 +25887,7 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="928" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:5">
       <c r="A928">
         <v>926</v>
       </c>
@@ -25848,7 +25904,7 @@
         <v>2783</v>
       </c>
     </row>
-    <row r="929" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:5">
       <c r="A929">
         <v>927</v>
       </c>
@@ -25865,7 +25921,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="930" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:5">
       <c r="A930">
         <v>928</v>
       </c>
@@ -25882,7 +25938,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="931" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:5">
       <c r="A931">
         <v>929</v>
       </c>
@@ -25899,7 +25955,7 @@
         <v>2792</v>
       </c>
     </row>
-    <row r="932" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:5">
       <c r="A932">
         <v>930</v>
       </c>
@@ -25916,7 +25972,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="933" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:5">
       <c r="A933">
         <v>931</v>
       </c>
@@ -25933,7 +25989,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="934" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:5">
       <c r="A934">
         <v>932</v>
       </c>
@@ -25950,7 +26006,7 @@
         <v>2801</v>
       </c>
     </row>
-    <row r="935" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:5">
       <c r="A935">
         <v>933</v>
       </c>
@@ -25967,7 +26023,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="936" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:5">
       <c r="A936">
         <v>934</v>
       </c>
@@ -25984,7 +26040,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="937" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:5">
       <c r="A937">
         <v>935</v>
       </c>
@@ -26001,7 +26057,7 @@
         <v>2810</v>
       </c>
     </row>
-    <row r="938" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:5">
       <c r="A938">
         <v>936</v>
       </c>
@@ -26018,7 +26074,7 @@
         <v>2813</v>
       </c>
     </row>
-    <row r="939" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:5">
       <c r="A939">
         <v>937</v>
       </c>
@@ -26035,7 +26091,7 @@
         <v>2816</v>
       </c>
     </row>
-    <row r="940" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:5">
       <c r="A940">
         <v>938</v>
       </c>
@@ -26052,7 +26108,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="941" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:5">
       <c r="A941">
         <v>939</v>
       </c>
@@ -26069,7 +26125,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="942" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:5">
       <c r="A942">
         <v>940</v>
       </c>
@@ -26086,7 +26142,7 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="943" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:5">
       <c r="A943">
         <v>941</v>
       </c>
@@ -26103,7 +26159,7 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="944" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:5">
       <c r="A944">
         <v>942</v>
       </c>
@@ -26120,7 +26176,7 @@
         <v>2831</v>
       </c>
     </row>
-    <row r="945" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:5">
       <c r="A945">
         <v>943</v>
       </c>
@@ -26137,7 +26193,7 @@
         <v>2834</v>
       </c>
     </row>
-    <row r="946" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:5">
       <c r="A946">
         <v>944</v>
       </c>
@@ -26154,7 +26210,7 @@
         <v>2837</v>
       </c>
     </row>
-    <row r="947" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:5">
       <c r="A947">
         <v>945</v>
       </c>
@@ -26171,7 +26227,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="948" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:5">
       <c r="A948">
         <v>946</v>
       </c>
@@ -26188,7 +26244,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="949" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:5">
       <c r="A949">
         <v>947</v>
       </c>
@@ -26205,7 +26261,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="950" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:5">
       <c r="A950">
         <v>948</v>
       </c>
@@ -26222,7 +26278,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="951" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:5">
       <c r="A951">
         <v>949</v>
       </c>
@@ -26239,7 +26295,7 @@
         <v>2852</v>
       </c>
     </row>
-    <row r="952" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:5">
       <c r="A952">
         <v>950</v>
       </c>
@@ -26256,7 +26312,7 @@
         <v>2855</v>
       </c>
     </row>
-    <row r="953" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:5">
       <c r="A953">
         <v>951</v>
       </c>
@@ -26273,7 +26329,7 @@
         <v>2858</v>
       </c>
     </row>
-    <row r="954" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:5">
       <c r="A954">
         <v>952</v>
       </c>
@@ -26290,7 +26346,7 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="955" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:5">
       <c r="A955">
         <v>953</v>
       </c>
@@ -26307,7 +26363,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="956" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:5">
       <c r="A956">
         <v>954</v>
       </c>
@@ -26324,7 +26380,7 @@
         <v>2867</v>
       </c>
     </row>
-    <row r="957" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:5">
       <c r="A957">
         <v>955</v>
       </c>
@@ -26341,7 +26397,7 @@
         <v>2870</v>
       </c>
     </row>
-    <row r="958" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:5">
       <c r="A958">
         <v>956</v>
       </c>
@@ -26358,7 +26414,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="959" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:5">
       <c r="A959">
         <v>957</v>
       </c>
@@ -26375,7 +26431,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="960" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:5">
       <c r="A960">
         <v>958</v>
       </c>
@@ -26392,7 +26448,7 @@
         <v>2879</v>
       </c>
     </row>
-    <row r="961" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:6">
       <c r="A961">
         <v>959</v>
       </c>
@@ -26409,7 +26465,7 @@
         <v>2882</v>
       </c>
     </row>
-    <row r="962" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:6">
       <c r="A962">
         <v>960</v>
       </c>
@@ -26429,7 +26485,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="963" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:6">
       <c r="A963">
         <v>961</v>
       </c>
@@ -26446,7 +26502,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="964" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:6">
       <c r="A964">
         <v>962</v>
       </c>
@@ -26463,7 +26519,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="965" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:6">
       <c r="A965">
         <v>963</v>
       </c>
@@ -26480,7 +26536,7 @@
         <v>2894</v>
       </c>
     </row>
-    <row r="966" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:6">
       <c r="A966">
         <v>964</v>
       </c>
@@ -26497,7 +26553,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="967" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:6">
       <c r="A967">
         <v>965</v>
       </c>
@@ -26514,7 +26570,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="968" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:6">
       <c r="A968">
         <v>966</v>
       </c>
@@ -26531,7 +26587,7 @@
         <v>2903</v>
       </c>
     </row>
-    <row r="969" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:6">
       <c r="A969">
         <v>967</v>
       </c>
@@ -26548,7 +26604,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="970" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:6">
       <c r="A970">
         <v>968</v>
       </c>
@@ -26565,7 +26621,7 @@
         <v>2909</v>
       </c>
     </row>
-    <row r="971" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:6">
       <c r="A971">
         <v>969</v>
       </c>
@@ -26582,7 +26638,7 @@
         <v>2912</v>
       </c>
     </row>
-    <row r="972" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:6">
       <c r="A972">
         <v>970</v>
       </c>
@@ -26599,7 +26655,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="973" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:6">
       <c r="A973">
         <v>971</v>
       </c>
@@ -26616,7 +26672,7 @@
         <v>2918</v>
       </c>
     </row>
-    <row r="974" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:6">
       <c r="A974">
         <v>972</v>
       </c>
@@ -26633,7 +26689,7 @@
         <v>2921</v>
       </c>
     </row>
-    <row r="975" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:6">
       <c r="A975">
         <v>973</v>
       </c>
@@ -26650,7 +26706,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="976" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:6">
       <c r="A976">
         <v>974</v>
       </c>
@@ -26667,7 +26723,7 @@
         <v>2927</v>
       </c>
     </row>
-    <row r="977" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:5">
       <c r="A977">
         <v>975</v>
       </c>
@@ -26684,7 +26740,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="978" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:5">
       <c r="A978">
         <v>976</v>
       </c>
@@ -26701,7 +26757,7 @@
         <v>531837457726680</v>
       </c>
     </row>
-    <row r="979" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:5">
       <c r="A979">
         <v>977</v>
       </c>
@@ -26718,7 +26774,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="980" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:5">
       <c r="A980">
         <v>978</v>
       </c>
@@ -26735,7 +26791,7 @@
         <v>2938</v>
       </c>
     </row>
-    <row r="981" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:5">
       <c r="A981">
         <v>979</v>
       </c>
@@ -26752,7 +26808,7 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="982" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:5">
       <c r="A982">
         <v>980</v>
       </c>
@@ -26769,7 +26825,7 @@
         <v>2944</v>
       </c>
     </row>
-    <row r="983" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:5">
       <c r="A983">
         <v>981</v>
       </c>
@@ -26786,7 +26842,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="984" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:5">
       <c r="A984">
         <v>982</v>
       </c>
@@ -26803,7 +26859,7 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="985" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:5">
       <c r="A985">
         <v>983</v>
       </c>
@@ -26820,7 +26876,7 @@
         <v>2953</v>
       </c>
     </row>
-    <row r="986" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:5">
       <c r="A986">
         <v>984</v>
       </c>
@@ -26837,7 +26893,7 @@
         <v>2956</v>
       </c>
     </row>
-    <row r="987" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:5">
       <c r="A987">
         <v>985</v>
       </c>
@@ -26854,7 +26910,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="988" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:5">
       <c r="A988">
         <v>986</v>
       </c>
@@ -26871,7 +26927,7 @@
         <v>2962</v>
       </c>
     </row>
-    <row r="989" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:5">
       <c r="A989">
         <v>987</v>
       </c>
@@ -26888,7 +26944,7 @@
         <v>2965</v>
       </c>
     </row>
-    <row r="990" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="990" spans="1:5">
       <c r="A990">
         <v>988</v>
       </c>
@@ -26905,7 +26961,7 @@
         <v>2968</v>
       </c>
     </row>
-    <row r="991" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:5">
       <c r="A991">
         <v>989</v>
       </c>
@@ -26922,7 +26978,7 @@
         <v>2971</v>
       </c>
     </row>
-    <row r="992" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:5">
       <c r="A992">
         <v>990</v>
       </c>
@@ -26939,7 +26995,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="993" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:5">
       <c r="A993">
         <v>991</v>
       </c>
@@ -26956,7 +27012,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="994" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:5">
       <c r="A994">
         <v>992</v>
       </c>
@@ -26973,7 +27029,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="995" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:5">
       <c r="A995">
         <v>993</v>
       </c>
@@ -26990,7 +27046,7 @@
         <v>2983</v>
       </c>
     </row>
-    <row r="996" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:5">
       <c r="A996">
         <v>994</v>
       </c>
@@ -27007,7 +27063,7 @@
         <v>2986</v>
       </c>
     </row>
-    <row r="997" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:5">
       <c r="A997">
         <v>995</v>
       </c>
@@ -27024,7 +27080,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="998" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:5">
       <c r="A998">
         <v>996</v>
       </c>
@@ -27041,7 +27097,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="999" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="999" spans="1:5">
       <c r="A999">
         <v>997</v>
       </c>
@@ -27058,7 +27114,7 @@
         <v>2995</v>
       </c>
     </row>
-    <row r="1000" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:5">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -27075,7 +27131,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="1001" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1001" spans="1:5">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -27092,7 +27148,7 @@
         <v>3001</v>
       </c>
     </row>
-    <row r="1002" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:5">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -27109,7 +27165,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="1003" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1003" spans="1:5">
       <c r="A1003">
         <v>1001</v>
       </c>
@@ -27126,7 +27182,7 @@
         <v>3007</v>
       </c>
     </row>
-    <row r="1004" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1004" spans="1:5">
       <c r="A1004">
         <v>1002</v>
       </c>
@@ -27143,7 +27199,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="1005" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1005" spans="1:5">
       <c r="A1005">
         <v>1003</v>
       </c>
@@ -27160,7 +27216,7 @@
         <v>3013</v>
       </c>
     </row>
-    <row r="1006" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:5">
       <c r="A1006">
         <v>1004</v>
       </c>
@@ -27177,7 +27233,7 @@
         <v>3016</v>
       </c>
     </row>
-    <row r="1007" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:5">
       <c r="A1007">
         <v>1005</v>
       </c>
@@ -27194,7 +27250,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="1008" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:5">
       <c r="A1008">
         <v>1006</v>
       </c>
@@ -27211,7 +27267,7 @@
         <v>3022</v>
       </c>
     </row>
-    <row r="1009" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:5">
       <c r="A1009">
         <v>1007</v>
       </c>
@@ -27228,7 +27284,7 @@
         <v>3025</v>
       </c>
     </row>
-    <row r="1010" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:5">
       <c r="A1010">
         <v>1008</v>
       </c>
@@ -27245,7 +27301,7 @@
         <v>3028</v>
       </c>
     </row>
-    <row r="1011" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:5">
       <c r="A1011">
         <v>1009</v>
       </c>
@@ -27262,7 +27318,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="1012" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1012" spans="1:5">
       <c r="A1012">
         <v>1010</v>
       </c>
@@ -27279,7 +27335,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="1013" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1013" spans="1:5">
       <c r="A1013">
         <v>1011</v>
       </c>
@@ -27296,7 +27352,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="1014" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:5">
       <c r="A1014">
         <v>1012</v>
       </c>
@@ -27313,7 +27369,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="1015" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:5">
       <c r="A1015">
         <v>1013</v>
       </c>
@@ -27330,7 +27386,7 @@
         <v>3043</v>
       </c>
     </row>
-    <row r="1016" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:5">
       <c r="A1016">
         <v>1014</v>
       </c>
@@ -27347,7 +27403,7 @@
         <v>3046</v>
       </c>
     </row>
-    <row r="1017" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:5">
       <c r="A1017">
         <v>1015</v>
       </c>
@@ -27364,7 +27420,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="1018" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:5">
       <c r="A1018">
         <v>1016</v>
       </c>
@@ -27381,7 +27437,7 @@
         <v>3052</v>
       </c>
     </row>
-    <row r="1019" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:5">
       <c r="A1019">
         <v>1017</v>
       </c>
@@ -27398,7 +27454,7 @@
         <v>3055</v>
       </c>
     </row>
-    <row r="1020" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1020" spans="1:5">
       <c r="A1020">
         <v>1018</v>
       </c>
@@ -27415,7 +27471,7 @@
         <v>3058</v>
       </c>
     </row>
-    <row r="1021" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1021" spans="1:5">
       <c r="A1021">
         <v>1019</v>
       </c>
@@ -27432,7 +27488,7 @@
         <v>3061</v>
       </c>
     </row>
-    <row r="1022" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1022" spans="1:5">
       <c r="A1022">
         <v>1020</v>
       </c>
@@ -27449,7 +27505,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="1023" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1023" spans="1:5">
       <c r="A1023">
         <v>1021</v>
       </c>
@@ -27466,7 +27522,7 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="1024" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1024" spans="1:5">
       <c r="A1024">
         <v>1022</v>
       </c>
@@ -27483,7 +27539,7 @@
         <v>3070</v>
       </c>
     </row>
-    <row r="1025" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1025" spans="1:6">
       <c r="A1025">
         <v>1023</v>
       </c>
@@ -27500,7 +27556,7 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="1028" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:6">
       <c r="A1028" s="10" t="s">
         <v>3089</v>
       </c>
@@ -27510,7 +27566,7 @@
       <c r="E1028" s="11"/>
       <c r="F1028" s="12"/>
     </row>
-    <row r="1029" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:6">
       <c r="A1029" t="s">
         <v>3075</v>
       </c>
@@ -27530,7 +27586,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="1030" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:6">
       <c r="A1030">
         <v>4</v>
       </c>
@@ -27553,7 +27609,7 @@
         <v>1.257285475730896E-4</v>
       </c>
     </row>
-    <row r="1041" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:8">
       <c r="A1041" s="10" t="s">
         <v>3088</v>
       </c>
@@ -27564,7 +27620,7 @@
       <c r="F1041" s="11"/>
       <c r="G1041" s="12"/>
     </row>
-    <row r="1042" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:8">
       <c r="A1042" t="s">
         <v>3081</v>
       </c>
@@ -27590,7 +27646,7 @@
         <v>3090</v>
       </c>
     </row>
-    <row r="1043" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:8">
       <c r="A1043">
         <v>14</v>
       </c>
@@ -27623,7 +27679,7 @@
         <v>4.8828125000005551E-4</v>
       </c>
     </row>
-    <row r="1044" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:8">
       <c r="A1044">
         <v>14</v>
       </c>
@@ -27656,7 +27712,7 @@
         <v>1.2207031250005551E-4</v>
       </c>
     </row>
-    <row r="1045" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:8">
       <c r="A1045">
         <v>20</v>
       </c>
@@ -27689,7 +27745,7 @@
         <v>2.3282020331068849E-10</v>
       </c>
     </row>
-    <row r="1046" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:8">
       <c r="A1046">
         <v>20</v>
       </c>
@@ -27722,17 +27778,17 @@
         <v>6.8780082577543991E-4</v>
       </c>
     </row>
-    <row r="1047" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1047" spans="1:8">
       <c r="E1047" s="7"/>
       <c r="G1047" s="4"/>
     </row>
-    <row r="1048" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1048" spans="1:8">
       <c r="A1048">
         <f>2^-6</f>
         <v>1.5625E-2</v>
       </c>
     </row>
-    <row r="1050" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:8">
       <c r="A1050" s="10" t="s">
         <v>3124</v>
       </c>
@@ -27743,7 +27799,7 @@
       <c r="F1050" s="11"/>
       <c r="G1050" s="12"/>
     </row>
-    <row r="1051" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:8">
       <c r="C1051" t="s">
         <v>3116</v>
       </c>
@@ -27751,7 +27807,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="1052" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:8">
       <c r="C1052">
         <v>976</v>
       </c>
@@ -27762,12 +27818,12 @@
         <v>3118</v>
       </c>
     </row>
-    <row r="1053" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1053" spans="1:8">
       <c r="A1053" t="s">
         <v>3121</v>
       </c>
     </row>
-    <row r="1054" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:8">
       <c r="A1054" t="s">
         <v>3092</v>
       </c>
@@ -27782,7 +27838,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1055" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1055" spans="1:8">
       <c r="A1055" t="s">
         <v>3093</v>
       </c>
@@ -27807,7 +27863,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="1056" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:8">
       <c r="A1056" t="s">
         <v>3094</v>
       </c>
@@ -27822,7 +27878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:7">
       <c r="A1057" t="s">
         <v>3095</v>
       </c>
@@ -27844,7 +27900,7 @@
         <v>2097152</v>
       </c>
     </row>
-    <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1058" spans="1:7">
       <c r="A1058" t="s">
         <v>3096</v>
       </c>
@@ -27859,7 +27915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1059" spans="1:7">
       <c r="A1059" t="s">
         <v>3097</v>
       </c>
@@ -27881,7 +27937,7 @@
         <v>67108864</v>
       </c>
     </row>
-    <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1060" spans="1:7">
       <c r="A1060" t="s">
         <v>3098</v>
       </c>
@@ -27896,7 +27952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1061" spans="1:7">
       <c r="A1061" t="s">
         <v>3099</v>
       </c>
@@ -27918,7 +27974,7 @@
         <v>1073741824</v>
       </c>
     </row>
-    <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1062" spans="1:7">
       <c r="A1062" t="s">
         <v>3100</v>
       </c>
@@ -27937,7 +27993,7 @@
         <v>531837210329088</v>
       </c>
     </row>
-    <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1063" spans="1:7">
       <c r="F1063" t="s">
         <v>3119</v>
       </c>
@@ -27945,7 +28001,7 @@
         <v>531837457726680</v>
       </c>
     </row>
-    <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:7">
       <c r="A1064" t="s">
         <v>3120</v>
       </c>
@@ -27954,7 +28010,7 @@
         <v>241946865740328</v>
       </c>
     </row>
-    <row r="1065" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1065" spans="1:7">
       <c r="A1065" t="s">
         <v>3079</v>
       </c>
@@ -27963,15 +28019,15 @@
         <v>0.32472550354327395</v>
       </c>
     </row>
-    <row r="1066" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1066" spans="1:7">
       <c r="D1066" s="2"/>
     </row>
-    <row r="1068" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:7">
       <c r="C1068" s="9">
         <v>531837457726680</v>
       </c>
     </row>
-    <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1072" spans="1:7">
       <c r="A1072">
         <v>-0.75</v>
       </c>
@@ -27983,7 +28039,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="1073" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:5">
       <c r="A1073">
         <v>-0.65625</v>
       </c>
@@ -27997,6 +28053,105 @@
       <c r="E1073">
         <f>B1072+B1072*(A1073-A1072)+B1072/2*(A1073-A1072)^2+B1072/6*(A1073-A1072)^3+B1072/24*(A1073-A1072)^4</f>
         <v>0.5187931366952474</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5" ht="15">
+      <c r="A1078" s="13" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5">
+      <c r="C1079" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5">
+      <c r="A1080" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1080">
+        <v>969774</v>
+      </c>
+      <c r="D1080" s="14">
+        <f>ROUNDDOWN(C1080/2^16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="E1080">
+        <f>ROUNDDOWN(C1080/2^14,0)</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5">
+      <c r="A1081" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1081">
+        <v>59855117</v>
+      </c>
+      <c r="D1081" s="14">
+        <f>ROUNDDOWN(C1081/2^16,0)</f>
+        <v>913</v>
+      </c>
+      <c r="E1081">
+        <f>ROUNDDOWN(C1081/2^14,0)</f>
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5">
+      <c r="A1082" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1082">
+        <f>C1080/C1081</f>
+        <v>1.6202023295685816E-2</v>
+      </c>
+      <c r="D1082">
+        <f>D1080/D1081</f>
+        <v>1.5334063526834611E-2</v>
+      </c>
+      <c r="E1082">
+        <f>E1080/E1081</f>
+        <v>1.6151108677799068E-2</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5">
+      <c r="B1083" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1083">
+        <v>1</v>
+      </c>
+      <c r="D1083">
+        <v>0</v>
+      </c>
+      <c r="E1083">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:5">
+      <c r="B1086" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1086">
+        <f>1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5">
+      <c r="B1087" t="s">
+        <v>3135</v>
       </c>
     </row>
   </sheetData>

--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8b65b6adf7979/桌面/Github File/IC_Design_Laboratory/HW5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="503" documentId="11_1B85D0BDD370594FA3B82111595ED87656CB84C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E8EEAA7-F43D-4855-879D-B5987E5E595E}"/>
+  <xr:revisionPtr revIDLastSave="518" documentId="11_1B85D0BDD370594FA3B82111595ED87656CB84C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B320B9E-173E-4FED-B3E4-F279406CC2FE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="3137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="3137">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -9666,11 +9666,11 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -9978,7 +9978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1087"/>
+  <dimension ref="A1:H1097"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
@@ -27557,14 +27557,14 @@
       </c>
     </row>
     <row r="1028" spans="1:6">
-      <c r="A1028" s="10" t="s">
+      <c r="A1028" s="12" t="s">
         <v>3089</v>
       </c>
-      <c r="B1028" s="11"/>
-      <c r="C1028" s="11"/>
-      <c r="D1028" s="11"/>
-      <c r="E1028" s="11"/>
-      <c r="F1028" s="12"/>
+      <c r="B1028" s="13"/>
+      <c r="C1028" s="13"/>
+      <c r="D1028" s="13"/>
+      <c r="E1028" s="13"/>
+      <c r="F1028" s="14"/>
     </row>
     <row r="1029" spans="1:6">
       <c r="A1029" t="s">
@@ -27610,15 +27610,15 @@
       </c>
     </row>
     <row r="1041" spans="1:8">
-      <c r="A1041" s="10" t="s">
+      <c r="A1041" s="12" t="s">
         <v>3088</v>
       </c>
-      <c r="B1041" s="11"/>
-      <c r="C1041" s="11"/>
-      <c r="D1041" s="11"/>
-      <c r="E1041" s="11"/>
-      <c r="F1041" s="11"/>
-      <c r="G1041" s="12"/>
+      <c r="B1041" s="13"/>
+      <c r="C1041" s="13"/>
+      <c r="D1041" s="13"/>
+      <c r="E1041" s="13"/>
+      <c r="F1041" s="13"/>
+      <c r="G1041" s="14"/>
     </row>
     <row r="1042" spans="1:8">
       <c r="A1042" t="s">
@@ -27789,15 +27789,15 @@
       </c>
     </row>
     <row r="1050" spans="1:8">
-      <c r="A1050" s="10" t="s">
+      <c r="A1050" s="12" t="s">
         <v>3124</v>
       </c>
-      <c r="B1050" s="11"/>
-      <c r="C1050" s="11"/>
-      <c r="D1050" s="11"/>
-      <c r="E1050" s="11"/>
-      <c r="F1050" s="11"/>
-      <c r="G1050" s="12"/>
+      <c r="B1050" s="13"/>
+      <c r="C1050" s="13"/>
+      <c r="D1050" s="13"/>
+      <c r="E1050" s="13"/>
+      <c r="F1050" s="13"/>
+      <c r="G1050" s="14"/>
     </row>
     <row r="1051" spans="1:8">
       <c r="C1051" t="s">
@@ -28056,7 +28056,7 @@
       </c>
     </row>
     <row r="1078" spans="1:5" ht="15">
-      <c r="A1078" s="13" t="s">
+      <c r="A1078" s="10" t="s">
         <v>3125</v>
       </c>
     </row>
@@ -28081,7 +28081,7 @@
       <c r="C1080">
         <v>969774</v>
       </c>
-      <c r="D1080" s="14">
+      <c r="D1080" s="11">
         <f>ROUNDDOWN(C1080/2^16,0)</f>
         <v>14</v>
       </c>
@@ -28100,7 +28100,7 @@
       <c r="C1081">
         <v>59855117</v>
       </c>
-      <c r="D1081" s="14">
+      <c r="D1081" s="11">
         <f>ROUNDDOWN(C1081/2^16,0)</f>
         <v>913</v>
       </c>
@@ -28131,12 +28131,15 @@
         <v>3136</v>
       </c>
       <c r="C1083">
+        <f>ROUNDDOWN(C1082/C1086,0)</f>
         <v>1</v>
       </c>
       <c r="D1083">
+        <f>ROUNDDOWN(D1082/D1086,0)</f>
         <v>0</v>
       </c>
       <c r="E1083">
+        <f>ROUNDDOWN(E1082/E1086,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -28148,9 +28151,122 @@
         <f>1/2^6</f>
         <v>1.5625E-2</v>
       </c>
+      <c r="D1086">
+        <f t="shared" ref="D1086:E1086" si="7">1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="E1086">
+        <f t="shared" si="7"/>
+        <v>1.5625E-2</v>
+      </c>
     </row>
     <row r="1087" spans="1:5">
       <c r="B1087" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5">
+      <c r="C1089" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5">
+      <c r="A1090" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1090">
+        <v>1284742</v>
+      </c>
+      <c r="D1090" s="11">
+        <f>ROUNDDOWN(C1090/2^16,0)</f>
+        <v>19</v>
+      </c>
+      <c r="E1090">
+        <f>ROUNDDOWN(C1090/2^14,0)</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:5">
+      <c r="A1091" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1091">
+        <v>59855117</v>
+      </c>
+      <c r="D1091" s="11">
+        <f>ROUNDDOWN(C1091/2^16,0)</f>
+        <v>913</v>
+      </c>
+      <c r="E1091">
+        <f>ROUNDDOWN(C1091/2^14,0)</f>
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:5">
+      <c r="A1092" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1092">
+        <f>C1090/C1091</f>
+        <v>2.1464196619981547E-2</v>
+      </c>
+      <c r="D1092">
+        <f>D1090/D1091</f>
+        <v>2.0810514786418401E-2</v>
+      </c>
+      <c r="E1092">
+        <f>E1090/E1091</f>
+        <v>2.1352313167259787E-2</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:5">
+      <c r="B1093" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1093">
+        <f>ROUNDDOWN(C1092/C1096,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D1093">
+        <f t="shared" ref="D1093:E1093" si="8">ROUNDDOWN(D1092/D1096,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E1093">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:5">
+      <c r="B1096" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1096">
+        <f>1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="D1096">
+        <f t="shared" ref="D1096:E1096" si="9">1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="E1096">
+        <f t="shared" si="9"/>
+        <v>1.5625E-2</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5">
+      <c r="B1097" t="s">
         <v>3135</v>
       </c>
     </row>

--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8b65b6adf7979/桌面/Github File/IC_Design_Laboratory/HW5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesse\OneDrive\桌面\Github File\IC_Design_Laboratory\HW5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="518" documentId="11_1B85D0BDD370594FA3B82111595ED87656CB84C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B320B9E-173E-4FED-B3E4-F279406CC2FE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C7EDB0-20DF-40A0-8151-8FE3E2386A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="3137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="3139">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -9506,6 +9506,14 @@
   </si>
   <si>
     <t>除法器輸出值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-bit fraction</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9687,10 +9695,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9978,7 +9982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1097"/>
+  <dimension ref="A1:H1107"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
@@ -9987,7 +9991,7 @@
     <col min="4" max="4" width="27.8984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.8984375" customWidth="1"/>
-    <col min="7" max="7" width="49.8984375" customWidth="1"/>
+    <col min="7" max="7" width="27.69921875" customWidth="1"/>
     <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -28165,7 +28169,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="1089" spans="1:5">
+    <row r="1089" spans="1:7">
       <c r="C1089" t="s">
         <v>3132</v>
       </c>
@@ -28176,7 +28180,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="1090" spans="1:5">
+    <row r="1090" spans="1:7">
       <c r="A1090" t="s">
         <v>3127</v>
       </c>
@@ -28195,7 +28199,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="1091" spans="1:5">
+    <row r="1091" spans="1:7">
       <c r="A1091" t="s">
         <v>3126</v>
       </c>
@@ -28214,7 +28218,7 @@
         <v>3653</v>
       </c>
     </row>
-    <row r="1092" spans="1:5">
+    <row r="1092" spans="1:7">
       <c r="A1092" t="s">
         <v>3128</v>
       </c>
@@ -28231,7 +28235,7 @@
         <v>2.1352313167259787E-2</v>
       </c>
     </row>
-    <row r="1093" spans="1:5">
+    <row r="1093" spans="1:7">
       <c r="B1093" t="s">
         <v>3136</v>
       </c>
@@ -28248,7 +28252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1096" spans="1:5">
+    <row r="1096" spans="1:7">
       <c r="B1096" t="s">
         <v>3133</v>
       </c>
@@ -28265,8 +28269,159 @@
         <v>1.5625E-2</v>
       </c>
     </row>
-    <row r="1097" spans="1:5">
+    <row r="1097" spans="1:7">
       <c r="B1097" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:7">
+      <c r="C1099" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>3134</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>3137</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:7">
+      <c r="A1100" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1100">
+        <v>969774</v>
+      </c>
+      <c r="D1100" s="11">
+        <f>ROUNDDOWN(C1100/2^16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="E1100">
+        <f>ROUNDDOWN(C1100/2^14,0)</f>
+        <v>59</v>
+      </c>
+      <c r="F1100">
+        <f>ROUNDDOWN(C1100/2^12,0)</f>
+        <v>236</v>
+      </c>
+      <c r="G1100">
+        <f>ROUNDDOWN(C1100/2^10,0)</f>
+        <v>947</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:7">
+      <c r="A1101" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1101">
+        <v>61952269</v>
+      </c>
+      <c r="D1101" s="11">
+        <f>ROUNDDOWN(C1101/2^16,0)</f>
+        <v>945</v>
+      </c>
+      <c r="E1101">
+        <f>ROUNDDOWN(C1101/2^14,0)</f>
+        <v>3781</v>
+      </c>
+      <c r="F1101">
+        <f>ROUNDDOWN(C1101/2^12,0)</f>
+        <v>15125</v>
+      </c>
+      <c r="G1101">
+        <f>ROUNDDOWN(C1101/2^10,0)</f>
+        <v>60500</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:7">
+      <c r="A1102" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1102">
+        <f>C1100/C1101</f>
+        <v>1.5653567103409885E-2</v>
+      </c>
+      <c r="D1102">
+        <f>D1100/D1101</f>
+        <v>1.4814814814814815E-2</v>
+      </c>
+      <c r="E1102">
+        <f>E1100/E1101</f>
+        <v>1.5604337476857974E-2</v>
+      </c>
+      <c r="F1102">
+        <f>F1100/F1101</f>
+        <v>1.5603305785123967E-2</v>
+      </c>
+      <c r="G1102">
+        <f>G1100/G1101</f>
+        <v>1.5652892561983472E-2</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:7">
+      <c r="B1103" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1103">
+        <f>ROUNDDOWN(C1102/C1106,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D1103">
+        <f t="shared" ref="D1103:G1103" si="10">ROUNDDOWN(D1102/D1106,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E1103">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F1103">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G1103">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1106" spans="2:7">
+      <c r="B1106" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1106">
+        <f>1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="D1106">
+        <f t="shared" ref="D1106:G1106" si="11">1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="E1106">
+        <f t="shared" si="11"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="F1106">
+        <f t="shared" si="11"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="G1106">
+        <f t="shared" si="11"/>
+        <v>1.5625E-2</v>
+      </c>
+    </row>
+    <row r="1107" spans="2:7">
+      <c r="B1107" t="s">
         <v>3135</v>
       </c>
     </row>

--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesse\OneDrive\桌面\Github File\IC_Design_Laboratory\HW5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C7EDB0-20DF-40A0-8151-8FE3E2386A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234ED1BE-6AC9-4BD7-9BD3-EDB688D6193B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="3139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3195" uniqueCount="3140">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -9514,6 +9514,10 @@
   </si>
   <si>
     <t>10-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12-bit fraction</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9982,7 +9986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1107"/>
+  <dimension ref="A1:H1117"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
@@ -9992,7 +9996,7 @@
     <col min="5" max="5" width="29.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.8984375" customWidth="1"/>
     <col min="7" max="7" width="27.69921875" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.19921875" customWidth="1"/>
     <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28395,7 +28399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1106" spans="2:7">
+    <row r="1106" spans="1:8">
       <c r="B1106" t="s">
         <v>3133</v>
       </c>
@@ -28420,8 +28424,182 @@
         <v>1.5625E-2</v>
       </c>
     </row>
-    <row r="1107" spans="2:7">
+    <row r="1107" spans="1:8">
       <c r="B1107" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:8">
+      <c r="C1109" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>3134</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>3137</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>3138</v>
+      </c>
+      <c r="H1109" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:8">
+      <c r="A1110" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1110">
+        <v>1346398</v>
+      </c>
+      <c r="D1110" s="11">
+        <f>ROUNDDOWN(C1110/2^16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="E1110">
+        <f>ROUNDDOWN(C1110/2^14,0)</f>
+        <v>82</v>
+      </c>
+      <c r="F1110">
+        <f>ROUNDDOWN(C1110/2^12,0)</f>
+        <v>328</v>
+      </c>
+      <c r="G1110">
+        <f>ROUNDDOWN(C1110/2^10,0)</f>
+        <v>1314</v>
+      </c>
+      <c r="H1110">
+        <f>ROUNDDOWN(C1110/2^8,0)</f>
+        <v>5259</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:8">
+      <c r="A1111" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1111">
+        <v>86141170</v>
+      </c>
+      <c r="D1111" s="11">
+        <f>ROUNDDOWN(C1111/2^16,0)</f>
+        <v>1314</v>
+      </c>
+      <c r="E1111">
+        <f>ROUNDDOWN(C1111/2^14,0)</f>
+        <v>5257</v>
+      </c>
+      <c r="F1111">
+        <f>ROUNDDOWN(C1111/2^12,0)</f>
+        <v>21030</v>
+      </c>
+      <c r="G1111">
+        <f>ROUNDDOWN(C1111/2^10,0)</f>
+        <v>84122</v>
+      </c>
+      <c r="H1111">
+        <f>ROUNDDOWN(C1111/2^8,0)</f>
+        <v>336488</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:8">
+      <c r="A1112" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1112">
+        <f>C1110/C1111</f>
+        <v>1.5630133651539677E-2</v>
+      </c>
+      <c r="D1112">
+        <f>D1110/D1111</f>
+        <v>1.5220700152207001E-2</v>
+      </c>
+      <c r="E1112">
+        <f>E1110/E1111</f>
+        <v>1.5598249952444359E-2</v>
+      </c>
+      <c r="F1112">
+        <f>F1110/F1111</f>
+        <v>1.5596766524013315E-2</v>
+      </c>
+      <c r="G1112">
+        <f>G1110/G1111</f>
+        <v>1.5620170704453056E-2</v>
+      </c>
+      <c r="H1112">
+        <f>H1110/H1111</f>
+        <v>1.562908632700126E-2</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:8">
+      <c r="B1113" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1113">
+        <f>ROUNDDOWN(C1112/C1116,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D1113">
+        <f t="shared" ref="D1113:H1113" si="12">ROUNDDOWN(D1112/D1116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E1113">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F1113">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="G1113">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H1113">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:8">
+      <c r="B1116" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1116">
+        <f>1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="D1116">
+        <f t="shared" ref="D1116:H1116" si="13">1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="E1116">
+        <f t="shared" si="13"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="F1116">
+        <f t="shared" si="13"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="G1116">
+        <f t="shared" si="13"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H1116">
+        <f t="shared" si="13"/>
+        <v>1.5625E-2</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:8">
+      <c r="B1117" t="s">
         <v>3135</v>
       </c>
     </row>

--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesse\OneDrive\桌面\Github File\IC_Design_Laboratory\HW5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234ED1BE-6AC9-4BD7-9BD3-EDB688D6193B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FB99B9-91E9-4E4D-8902-CEFA3EB5F2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3195" uniqueCount="3140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="3144">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -9518,6 +9518,22 @@
   </si>
   <si>
     <t>12-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pat60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pat62</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pat93</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>14-bit fraction</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9986,7 +10002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1117"/>
+  <dimension ref="A1:I1136"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
@@ -9997,7 +10013,7 @@
     <col min="6" max="6" width="15.8984375" customWidth="1"/>
     <col min="7" max="7" width="27.69921875" customWidth="1"/>
     <col min="8" max="8" width="19.19921875" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -28429,6 +28445,11 @@
         <v>3135</v>
       </c>
     </row>
+    <row r="1108" spans="1:8">
+      <c r="A1108" t="s">
+        <v>3140</v>
+      </c>
+    </row>
     <row r="1109" spans="1:8">
       <c r="C1109" t="s">
         <v>3132</v>
@@ -28516,27 +28537,27 @@
         <v>3128</v>
       </c>
       <c r="C1112">
-        <f>C1110/C1111</f>
+        <f t="shared" ref="C1112:H1112" si="12">C1110/C1111</f>
         <v>1.5630133651539677E-2</v>
       </c>
       <c r="D1112">
-        <f>D1110/D1111</f>
+        <f t="shared" si="12"/>
         <v>1.5220700152207001E-2</v>
       </c>
       <c r="E1112">
-        <f>E1110/E1111</f>
+        <f t="shared" si="12"/>
         <v>1.5598249952444359E-2</v>
       </c>
       <c r="F1112">
-        <f>F1110/F1111</f>
+        <f t="shared" si="12"/>
         <v>1.5596766524013315E-2</v>
       </c>
       <c r="G1112">
-        <f>G1110/G1111</f>
+        <f t="shared" si="12"/>
         <v>1.5620170704453056E-2</v>
       </c>
       <c r="H1112">
-        <f>H1110/H1111</f>
+        <f t="shared" si="12"/>
         <v>1.562908632700126E-2</v>
       </c>
     </row>
@@ -28549,23 +28570,23 @@
         <v>1</v>
       </c>
       <c r="D1113">
-        <f t="shared" ref="D1113:H1113" si="12">ROUNDDOWN(D1112/D1116,0)</f>
+        <f t="shared" ref="D1113:H1113" si="13">ROUNDDOWN(D1112/D1116,0)</f>
         <v>0</v>
       </c>
       <c r="E1113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F1113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G1113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H1113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -28578,29 +28599,400 @@
         <v>1.5625E-2</v>
       </c>
       <c r="D1116">
-        <f t="shared" ref="D1116:H1116" si="13">1/2^6</f>
+        <f t="shared" ref="D1116:H1116" si="14">1/2^6</f>
         <v>1.5625E-2</v>
       </c>
       <c r="E1116">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.5625E-2</v>
       </c>
       <c r="F1116">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.5625E-2</v>
       </c>
       <c r="G1116">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.5625E-2</v>
       </c>
       <c r="H1116">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.5625E-2</v>
       </c>
     </row>
     <row r="1117" spans="1:8">
       <c r="B1117" t="s">
         <v>3135</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:8">
+      <c r="A1119" t="s">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:8">
+      <c r="C1120" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D1120" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>3134</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>3137</v>
+      </c>
+      <c r="G1120" t="s">
+        <v>3138</v>
+      </c>
+      <c r="H1120" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:9">
+      <c r="A1121" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1121">
+        <v>1811776</v>
+      </c>
+      <c r="D1121" s="11">
+        <f>ROUNDDOWN(C1121/2^16,0)</f>
+        <v>27</v>
+      </c>
+      <c r="E1121">
+        <f>ROUNDDOWN(C1121/2^14,0)</f>
+        <v>110</v>
+      </c>
+      <c r="F1121">
+        <f>ROUNDDOWN(C1121/2^12,0)</f>
+        <v>442</v>
+      </c>
+      <c r="G1121">
+        <f>ROUNDDOWN(C1121/2^10,0)</f>
+        <v>1769</v>
+      </c>
+      <c r="H1121">
+        <f>ROUNDDOWN(C1121/2^8,0)</f>
+        <v>7077</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:9">
+      <c r="A1122" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1122">
+        <v>57974990</v>
+      </c>
+      <c r="D1122" s="11">
+        <f>ROUNDDOWN(C1122/2^16,0)</f>
+        <v>884</v>
+      </c>
+      <c r="E1122">
+        <f>ROUNDDOWN(C1122/2^14,0)</f>
+        <v>3538</v>
+      </c>
+      <c r="F1122">
+        <f>ROUNDDOWN(C1122/2^12,0)</f>
+        <v>14154</v>
+      </c>
+      <c r="G1122">
+        <f>ROUNDDOWN(C1122/2^10,0)</f>
+        <v>56616</v>
+      </c>
+      <c r="H1122">
+        <f>ROUNDDOWN(C1122/2^8,0)</f>
+        <v>226464</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:9">
+      <c r="A1123" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1123">
+        <f t="shared" ref="C1123" si="15">C1121/C1122</f>
+        <v>3.1250992885035425E-2</v>
+      </c>
+      <c r="D1123">
+        <f t="shared" ref="D1123" si="16">D1121/D1122</f>
+        <v>3.0542986425339366E-2</v>
+      </c>
+      <c r="E1123">
+        <f t="shared" ref="E1123" si="17">E1121/E1122</f>
+        <v>3.1091011871113624E-2</v>
+      </c>
+      <c r="F1123">
+        <f t="shared" ref="F1123" si="18">F1121/F1122</f>
+        <v>3.1227921435636571E-2</v>
+      </c>
+      <c r="G1123">
+        <f t="shared" ref="G1123" si="19">G1121/G1122</f>
+        <v>3.1245584287127315E-2</v>
+      </c>
+      <c r="H1123">
+        <f t="shared" ref="H1123" si="20">H1121/H1122</f>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:9">
+      <c r="B1124" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1124">
+        <f>ROUNDDOWN(C1123/C1127,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D1124">
+        <f t="shared" ref="D1124:H1124" si="21">ROUNDDOWN(D1123/D1127,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E1124">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F1124">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="G1124">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="H1124">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:9">
+      <c r="B1127" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1127">
+        <f>1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="D1127">
+        <f t="shared" ref="D1127:H1127" si="22">1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="E1127">
+        <f t="shared" si="22"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="F1127">
+        <f t="shared" si="22"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="G1127">
+        <f t="shared" si="22"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H1127">
+        <f t="shared" si="22"/>
+        <v>1.5625E-2</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:9">
+      <c r="A1128" t="s">
+        <v>3142</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:9">
+      <c r="C1129" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>3134</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>3137</v>
+      </c>
+      <c r="G1129" t="s">
+        <v>3138</v>
+      </c>
+      <c r="H1129" t="s">
+        <v>3139</v>
+      </c>
+      <c r="I1129" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:9">
+      <c r="A1130" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1130">
+        <v>4414669</v>
+      </c>
+      <c r="D1130" s="11">
+        <f>ROUNDDOWN(C1130/2^16,0)</f>
+        <v>67</v>
+      </c>
+      <c r="E1130">
+        <f>ROUNDDOWN(C1130/2^14,0)</f>
+        <v>269</v>
+      </c>
+      <c r="F1130">
+        <f>ROUNDDOWN(C1130/2^12,0)</f>
+        <v>1077</v>
+      </c>
+      <c r="G1130">
+        <f>ROUNDDOWN(C1130/2^10,0)</f>
+        <v>4311</v>
+      </c>
+      <c r="H1130">
+        <f>ROUNDDOWN(C1130/2^8,0)</f>
+        <v>17244</v>
+      </c>
+      <c r="I1130">
+        <f>ROUNDDOWN(C1130/2^6,0)</f>
+        <v>68979</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:9">
+      <c r="A1131" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1131">
+        <v>282532440</v>
+      </c>
+      <c r="D1131" s="11">
+        <f>ROUNDDOWN(C1131/2^16,0)</f>
+        <v>4311</v>
+      </c>
+      <c r="E1131">
+        <f>ROUNDDOWN(C1131/2^14,0)</f>
+        <v>17244</v>
+      </c>
+      <c r="F1131">
+        <f>ROUNDDOWN(C1131/2^12,0)</f>
+        <v>68977</v>
+      </c>
+      <c r="G1131">
+        <f>ROUNDDOWN(C1131/2^10,0)</f>
+        <v>275910</v>
+      </c>
+      <c r="H1131">
+        <f>ROUNDDOWN(C1131/2^8,0)</f>
+        <v>1103642</v>
+      </c>
+      <c r="I1131">
+        <f>ROUNDDOWN(C1131/2^6,0)</f>
+        <v>4414569</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:9">
+      <c r="A1132" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1132">
+        <f t="shared" ref="C1132" si="23">C1130/C1131</f>
+        <v>1.5625352614375893E-2</v>
+      </c>
+      <c r="D1132">
+        <f t="shared" ref="D1132" si="24">D1130/D1131</f>
+        <v>1.5541637671073997E-2</v>
+      </c>
+      <c r="E1132">
+        <f t="shared" ref="E1132" si="25">E1130/E1131</f>
+        <v>1.5599628856413824E-2</v>
+      </c>
+      <c r="F1132">
+        <f t="shared" ref="F1132" si="26">F1130/F1131</f>
+        <v>1.5613900285602448E-2</v>
+      </c>
+      <c r="G1132">
+        <f t="shared" ref="G1132" si="27">G1130/G1131</f>
+        <v>1.5624660215287594E-2</v>
+      </c>
+      <c r="H1132">
+        <f t="shared" ref="H1132:I1132" si="28">H1130/H1131</f>
+        <v>1.5624631900561958E-2</v>
+      </c>
+      <c r="I1132">
+        <f t="shared" si="28"/>
+        <v>1.5625307929267841E-2</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:9">
+      <c r="B1133" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1133">
+        <f>ROUNDDOWN(C1132/C1136,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D1133">
+        <f t="shared" ref="D1133:I1133" si="29">ROUNDDOWN(D1132/D1136,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E1133">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="F1133">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="G1133">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H1133">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I1133">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:9">
+      <c r="B1136" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1136">
+        <f>1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="D1136">
+        <f t="shared" ref="D1136:I1136" si="30">1/2^6</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="E1136">
+        <f t="shared" si="30"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="F1136">
+        <f t="shared" si="30"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="G1136">
+        <f t="shared" si="30"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="H1136">
+        <f t="shared" si="30"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="I1136">
+        <f t="shared" si="30"/>
+        <v>1.5625E-2</v>
       </c>
     </row>
   </sheetData>

--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesse\OneDrive\桌面\Github File\IC_Design_Laboratory\HW5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FB99B9-91E9-4E4D-8902-CEFA3EB5F2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C55829-4BB6-483F-A273-652FCA2F6947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="3144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="3165">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -9534,6 +9534,90 @@
   </si>
   <si>
     <t>14-bit fraction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sofftV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token32</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token33</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token41</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token43</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token48</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token51</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token53</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token54</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token55</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token56</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token57</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token58</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token59</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token61</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token62</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>token63</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -10002,7 +10086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1136"/>
+  <dimension ref="A1:I1213"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
@@ -28995,6 +29079,782 @@
         <v>1.5625E-2</v>
       </c>
     </row>
+    <row r="1140" spans="1:4">
+      <c r="A1140" t="s">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:4">
+      <c r="A1141">
+        <v>0</v>
+      </c>
+      <c r="D1141">
+        <f>A1141*B1141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:4">
+      <c r="A1142">
+        <v>0</v>
+      </c>
+      <c r="D1142">
+        <f t="shared" ref="D1142:D1205" si="31">A1142*B1142</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:4">
+      <c r="A1143">
+        <v>0</v>
+      </c>
+      <c r="D1143">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:4">
+      <c r="A1144">
+        <v>0</v>
+      </c>
+      <c r="D1144">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:4">
+      <c r="A1145">
+        <v>0</v>
+      </c>
+      <c r="D1145">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:4">
+      <c r="A1146">
+        <v>0</v>
+      </c>
+      <c r="D1146">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:4">
+      <c r="A1147">
+        <v>0</v>
+      </c>
+      <c r="D1147">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:4">
+      <c r="A1148">
+        <v>0</v>
+      </c>
+      <c r="D1148">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:4">
+      <c r="D1149">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:4">
+      <c r="A1150">
+        <v>0</v>
+      </c>
+      <c r="B1150">
+        <v>-6</v>
+      </c>
+      <c r="D1150">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:4">
+      <c r="A1151">
+        <v>0</v>
+      </c>
+      <c r="D1151">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:4">
+      <c r="A1152">
+        <v>0</v>
+      </c>
+      <c r="D1152">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4">
+      <c r="A1153">
+        <v>0</v>
+      </c>
+      <c r="D1153">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4">
+      <c r="A1154">
+        <v>0</v>
+      </c>
+      <c r="D1154">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4">
+      <c r="A1155">
+        <v>1</v>
+      </c>
+      <c r="B1155">
+        <v>9</v>
+      </c>
+      <c r="D1155">
+        <f t="shared" si="31"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4">
+      <c r="A1156">
+        <v>0</v>
+      </c>
+      <c r="D1156">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4">
+      <c r="A1157">
+        <v>0</v>
+      </c>
+      <c r="D1157">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4">
+      <c r="D1158">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4">
+      <c r="A1159">
+        <v>0</v>
+      </c>
+      <c r="D1159">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4">
+      <c r="A1160">
+        <v>0</v>
+      </c>
+      <c r="D1160">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4">
+      <c r="A1161">
+        <v>0</v>
+      </c>
+      <c r="D1161">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4">
+      <c r="A1162">
+        <v>0</v>
+      </c>
+      <c r="D1162">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4">
+      <c r="A1163">
+        <v>0</v>
+      </c>
+      <c r="D1163">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4">
+      <c r="A1164">
+        <v>0</v>
+      </c>
+      <c r="D1164">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4">
+      <c r="A1165">
+        <v>0</v>
+      </c>
+      <c r="D1165">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4">
+      <c r="A1166">
+        <v>0</v>
+      </c>
+      <c r="D1166">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4">
+      <c r="D1167">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4">
+      <c r="A1168">
+        <v>1</v>
+      </c>
+      <c r="B1168">
+        <v>3</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D1168">
+        <f t="shared" si="31"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4">
+      <c r="A1169">
+        <v>0</v>
+      </c>
+      <c r="B1169">
+        <v>17</v>
+      </c>
+      <c r="D1169">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4">
+      <c r="A1170">
+        <v>0</v>
+      </c>
+      <c r="B1170">
+        <v>-12</v>
+      </c>
+      <c r="D1170">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4">
+      <c r="A1171">
+        <v>0</v>
+      </c>
+      <c r="B1171">
+        <v>36</v>
+      </c>
+      <c r="D1171">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4">
+      <c r="A1172">
+        <v>0</v>
+      </c>
+      <c r="B1172">
+        <v>-5</v>
+      </c>
+      <c r="D1172">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4">
+      <c r="A1173">
+        <v>1</v>
+      </c>
+      <c r="B1173">
+        <v>7</v>
+      </c>
+      <c r="D1173">
+        <f t="shared" si="31"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4">
+      <c r="A1174">
+        <v>0</v>
+      </c>
+      <c r="B1174">
+        <v>-44</v>
+      </c>
+      <c r="D1174">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4">
+      <c r="A1175">
+        <v>0</v>
+      </c>
+      <c r="B1175">
+        <v>9</v>
+      </c>
+      <c r="D1175">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4">
+      <c r="D1176">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4">
+      <c r="A1177">
+        <v>1</v>
+      </c>
+      <c r="B1177">
+        <v>42</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>3146</v>
+      </c>
+      <c r="D1177">
+        <f t="shared" si="31"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4">
+      <c r="A1178">
+        <v>3</v>
+      </c>
+      <c r="B1178">
+        <v>-1</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>3147</v>
+      </c>
+      <c r="D1178">
+        <f t="shared" si="31"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4">
+      <c r="A1179">
+        <v>0</v>
+      </c>
+      <c r="B1179">
+        <v>-2</v>
+      </c>
+      <c r="D1179">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4">
+      <c r="A1180">
+        <v>0</v>
+      </c>
+      <c r="D1180">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4">
+      <c r="A1181">
+        <v>0</v>
+      </c>
+      <c r="D1181">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4">
+      <c r="A1182">
+        <v>0</v>
+      </c>
+      <c r="D1182">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4">
+      <c r="A1183">
+        <v>0</v>
+      </c>
+      <c r="D1183">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4">
+      <c r="A1184">
+        <v>0</v>
+      </c>
+      <c r="D1184">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4">
+      <c r="D1185">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4">
+      <c r="A1186">
+        <v>0</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>3148</v>
+      </c>
+      <c r="D1186">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4">
+      <c r="A1187">
+        <v>1</v>
+      </c>
+      <c r="B1187">
+        <v>-4</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>3149</v>
+      </c>
+      <c r="D1187">
+        <f t="shared" si="31"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4">
+      <c r="A1188">
+        <v>0</v>
+      </c>
+      <c r="D1188">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4">
+      <c r="A1189">
+        <v>1</v>
+      </c>
+      <c r="B1189">
+        <v>19</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>3150</v>
+      </c>
+      <c r="D1189">
+        <f t="shared" si="31"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4">
+      <c r="A1190">
+        <v>0</v>
+      </c>
+      <c r="D1190">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4">
+      <c r="A1191">
+        <v>0</v>
+      </c>
+      <c r="D1191">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4">
+      <c r="A1192">
+        <v>0</v>
+      </c>
+      <c r="D1192">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4">
+      <c r="A1193">
+        <v>0</v>
+      </c>
+      <c r="D1193">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4">
+      <c r="D1194">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4">
+      <c r="A1195">
+        <v>2</v>
+      </c>
+      <c r="B1195">
+        <v>-2</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>3151</v>
+      </c>
+      <c r="D1195">
+        <f t="shared" si="31"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4">
+      <c r="A1196">
+        <v>0</v>
+      </c>
+      <c r="D1196">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4">
+      <c r="A1197">
+        <v>5</v>
+      </c>
+      <c r="B1197">
+        <v>-19</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>3152</v>
+      </c>
+      <c r="D1197">
+        <f t="shared" si="31"/>
+        <v>-95</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4">
+      <c r="A1198">
+        <v>1</v>
+      </c>
+      <c r="B1198">
+        <v>-2</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>3153</v>
+      </c>
+      <c r="D1198">
+        <f t="shared" si="31"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4">
+      <c r="A1199">
+        <v>0</v>
+      </c>
+      <c r="D1199">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4">
+      <c r="A1200">
+        <v>1</v>
+      </c>
+      <c r="B1200">
+        <v>-1</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>3154</v>
+      </c>
+      <c r="D1200">
+        <f t="shared" si="31"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4">
+      <c r="A1201">
+        <v>2</v>
+      </c>
+      <c r="B1201">
+        <v>-9</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>3155</v>
+      </c>
+      <c r="D1201">
+        <f t="shared" si="31"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4">
+      <c r="A1202">
+        <v>2</v>
+      </c>
+      <c r="B1202">
+        <v>-6</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>3156</v>
+      </c>
+      <c r="D1202">
+        <f t="shared" si="31"/>
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4">
+      <c r="D1203">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4">
+      <c r="A1204">
+        <v>2</v>
+      </c>
+      <c r="B1204">
+        <v>-14</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>3157</v>
+      </c>
+      <c r="D1204">
+        <f t="shared" si="31"/>
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4">
+      <c r="A1205">
+        <v>1</v>
+      </c>
+      <c r="B1205">
+        <v>-2</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>3158</v>
+      </c>
+      <c r="D1205">
+        <f t="shared" si="31"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4">
+      <c r="A1206">
+        <v>2</v>
+      </c>
+      <c r="B1206">
+        <v>-18</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>3159</v>
+      </c>
+      <c r="D1206">
+        <f t="shared" ref="D1206:D1211" si="32">A1206*B1206</f>
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4">
+      <c r="A1207">
+        <v>1</v>
+      </c>
+      <c r="B1207">
+        <v>-14</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D1207">
+        <f t="shared" si="32"/>
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4">
+      <c r="A1208">
+        <v>1</v>
+      </c>
+      <c r="B1208">
+        <v>-8</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>3161</v>
+      </c>
+      <c r="D1208">
+        <f t="shared" si="32"/>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4">
+      <c r="A1209">
+        <v>2</v>
+      </c>
+      <c r="B1209">
+        <v>-5</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D1209">
+        <f t="shared" si="32"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4">
+      <c r="A1210">
+        <v>1</v>
+      </c>
+      <c r="B1210">
+        <v>-5</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D1210">
+        <f t="shared" si="32"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4">
+      <c r="A1211">
+        <v>2</v>
+      </c>
+      <c r="B1211">
+        <v>-1</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>3164</v>
+      </c>
+      <c r="D1211">
+        <f t="shared" si="32"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4">
+      <c r="D1213">
+        <f>SUM(D1141:D1211)</f>
+        <v>-164</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1041:G1041"/>

--- a/HW5/Softmax_table.xlsx
+++ b/HW5/Softmax_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesse\OneDrive\桌面\Github File\IC_Design_Laboratory\HW5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C55829-4BB6-483F-A273-652FCA2F6947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3692EB-D255-440B-B91D-0BDC6BA70CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="3165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="3166">
   <si>
     <t>Fixed-point Input (4Q6)</t>
   </si>
@@ -9618,6 +9618,10 @@
   </si>
   <si>
     <t>token63</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19-bit fraction</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9625,13 +9629,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="178" formatCode="0.0000%"/>
     <numFmt numFmtId="179" formatCode="0.0000000%"/>
     <numFmt numFmtId="180" formatCode="0.0000000"/>
     <numFmt numFmtId="181" formatCode="0.000000"/>
+    <numFmt numFmtId="200" formatCode="0.00000000000000000000_ "/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -9759,7 +9764,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -9783,6 +9788,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -10086,7 +10092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1213"/>
+  <dimension ref="A1:J1213"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.19921875" bestFit="1" customWidth="1"/>
@@ -10098,6 +10104,7 @@
     <col min="7" max="7" width="27.69921875" customWidth="1"/>
     <col min="8" max="8" width="19.19921875" customWidth="1"/>
     <col min="9" max="9" width="14.69921875" customWidth="1"/>
+    <col min="10" max="10" width="28.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -28733,7 +28740,7 @@
         <v>3139</v>
       </c>
     </row>
-    <row r="1121" spans="1:9">
+    <row r="1121" spans="1:10">
       <c r="A1121" t="s">
         <v>3127</v>
       </c>
@@ -28764,7 +28771,7 @@
         <v>7077</v>
       </c>
     </row>
-    <row r="1122" spans="1:9">
+    <row r="1122" spans="1:10">
       <c r="A1122" t="s">
         <v>3126</v>
       </c>
@@ -28795,7 +28802,7 @@
         <v>226464</v>
       </c>
     </row>
-    <row r="1123" spans="1:9">
+    <row r="1123" spans="1:10">
       <c r="A1123" t="s">
         <v>3128</v>
       </c>
@@ -28824,7 +28831,7 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="1124" spans="1:9">
+    <row r="1124" spans="1:10">
       <c r="B1124" t="s">
         <v>3136</v>
       </c>
@@ -28853,7 +28860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1127" spans="1:9">
+    <row r="1127" spans="1:10">
       <c r="B1127" t="s">
         <v>3133</v>
       </c>
@@ -28882,12 +28889,12 @@
         <v>1.5625E-2</v>
       </c>
     </row>
-    <row r="1128" spans="1:9">
+    <row r="1128" spans="1:10">
       <c r="A1128" t="s">
         <v>3142</v>
       </c>
     </row>
-    <row r="1129" spans="1:9">
+    <row r="1129" spans="1:10">
       <c r="C1129" t="s">
         <v>3132</v>
       </c>
@@ -28909,8 +28916,11 @@
       <c r="I1129" t="s">
         <v>3143</v>
       </c>
-    </row>
-    <row r="1130" spans="1:9">
+      <c r="J1129" t="s">
+        <v>3165</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:10">
       <c r="A1130" t="s">
         <v>3127</v>
       </c>
@@ -28944,8 +28954,12 @@
         <f>ROUNDDOWN(C1130/2^6,0)</f>
         <v>68979</v>
       </c>
-    </row>
-    <row r="1131" spans="1:9">
+      <c r="J1130">
+        <f>ROUNDDOWN(C1130/2^1,0)</f>
+        <v>2207334</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:10">
       <c r="A1131" t="s">
         <v>3126</v>
       </c>
@@ -28979,8 +28993,12 @@
         <f>ROUNDDOWN(C1131/2^6,0)</f>
         <v>4414569</v>
       </c>
-    </row>
-    <row r="1132" spans="1:9">
+      <c r="J1131">
+        <f>ROUNDDOWN(C1131/2^1,0)</f>
+        <v>141266220</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:10">
       <c r="A1132" t="s">
         <v>3128</v>
       </c>
@@ -29005,15 +29023,19 @@
         <v>1.5624660215287594E-2</v>
       </c>
       <c r="H1132">
-        <f t="shared" ref="H1132:I1132" si="28">H1130/H1131</f>
+        <f t="shared" ref="H1132:J1132" si="28">H1130/H1131</f>
         <v>1.5624631900561958E-2</v>
       </c>
       <c r="I1132">
         <f t="shared" si="28"/>
         <v>1.5625307929267841E-2</v>
       </c>
-    </row>
-    <row r="1133" spans="1:9">
+      <c r="J1132">
+        <f t="shared" si="28"/>
+        <v>1.562534907495932E-2</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:10">
       <c r="B1133" t="s">
         <v>3136</v>
       </c>
@@ -29022,7 +29044,7 @@
         <v>1</v>
       </c>
       <c r="D1133">
-        <f t="shared" ref="D1133:I1133" si="29">ROUNDDOWN(D1132/D1136,0)</f>
+        <f t="shared" ref="D1133:J1133" si="29">ROUNDDOWN(D1132/D1136,0)</f>
         <v>0</v>
       </c>
       <c r="E1133">
@@ -29045,8 +29067,12 @@
         <f t="shared" si="29"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="1136" spans="1:9">
+      <c r="J1133">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:10">
       <c r="B1136" t="s">
         <v>3133</v>
       </c>
@@ -29055,7 +29081,7 @@
         <v>1.5625E-2</v>
       </c>
       <c r="D1136">
-        <f t="shared" ref="D1136:I1136" si="30">1/2^6</f>
+        <f t="shared" ref="D1136:J1136" si="30">1/2^6</f>
         <v>1.5625E-2</v>
       </c>
       <c r="E1136">
@@ -29078,13 +29104,27 @@
         <f t="shared" si="30"/>
         <v>1.5625E-2</v>
       </c>
-    </row>
-    <row r="1140" spans="1:4">
+      <c r="J1136">
+        <f t="shared" si="30"/>
+        <v>1.5625E-2</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:10">
+      <c r="J1139" s="15">
+        <f>1/J1131</f>
+        <v>7.0788331421340499E-9</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:10">
       <c r="A1140" t="s">
         <v>3144</v>
       </c>
-    </row>
-    <row r="1141" spans="1:4">
+      <c r="J1140">
+        <f>ROUNDDOWN(1/J1131,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:10">
       <c r="A1141">
         <v>0</v>
       </c>
@@ -29093,7 +29133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1142" spans="1:4">
+    <row r="1142" spans="1:10">
       <c r="A1142">
         <v>0</v>
       </c>
@@ -29102,7 +29142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1143" spans="1:4">
+    <row r="1143" spans="1:10">
       <c r="A1143">
         <v>0</v>
       </c>
@@ -29111,7 +29151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1144" spans="1:4">
+    <row r="1144" spans="1:10">
       <c r="A1144">
         <v>0</v>
       </c>
@@ -29120,7 +29160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1145" spans="1:4">
+    <row r="1145" spans="1:10">
       <c r="A1145">
         <v>0</v>
       </c>
@@ -29129,7 +29169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1146" spans="1:4">
+    <row r="1146" spans="1:10">
       <c r="A1146">
         <v>0</v>
       </c>
@@ -29138,7 +29178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1147" spans="1:4">
+    <row r="1147" spans="1:10">
       <c r="A1147">
         <v>0</v>
       </c>
@@ -29147,7 +29187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1148" spans="1:4">
+    <row r="1148" spans="1:10">
       <c r="A1148">
         <v>0</v>
       </c>
@@ -29156,13 +29196,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1149" spans="1:4">
+    <row r="1149" spans="1:10">
       <c r="D1149">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
-    <row r="1150" spans="1:4">
+    <row r="1150" spans="1:10">
       <c r="A1150">
         <v>0</v>
       </c>
@@ -29174,7 +29214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1151" spans="1:4">
+    <row r="1151" spans="1:10">
       <c r="A1151">
         <v>0</v>
       </c>
@@ -29183,7 +29223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1152" spans="1:4">
+    <row r="1152" spans="1:10">
       <c r="A1152">
         <v>0</v>
       </c>
